--- a/2026_국토대장정_여행플래너.xlsx
+++ b/2026_국토대장정_여행플래너.xlsx
@@ -3463,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="86" min="1" max="1"/>
@@ -3865,37 +3865,32 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="87">
-      <c r="A12" s="198" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>교통</t>
         </is>
       </c>
-      <c r="B12" s="199" t="inlineStr">
-        <is>
-          <t>금오도 여객선 (왕복)</t>
-        </is>
-      </c>
-      <c r="C12" s="198" t="inlineStr">
-        <is>
-          <t>8/12</t>
-        </is>
-      </c>
-      <c r="D12" s="200" t="inlineStr">
-        <is>
-          <t>여수연안여객터미널 현장</t>
-        </is>
-      </c>
-      <c r="E12" s="200" t="inlineStr"/>
-      <c r="F12" s="200" t="inlineStr"/>
-      <c r="G12" s="200" t="inlineStr"/>
-      <c r="H12" s="199" t="inlineStr">
-        <is>
-          <t>시간표 미리 확인</t>
-        </is>
-      </c>
-      <c r="I12" s="198" t="inlineStr"/>
-      <c r="J12" s="198" t="inlineStr"/>
-      <c r="K12" s="198" t="inlineStr">
+      <c r="B12" s="86" t="inlineStr">
+        <is>
+          <t>KTX 신경주→부산역</t>
+        </is>
+      </c>
+      <c r="C12" s="86" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="D12" s="86" t="inlineStr">
+        <is>
+          <t>korail.com or 코레일 앱</t>
+        </is>
+      </c>
+      <c r="H12" s="86" t="inlineStr">
+        <is>
+          <t>경주 Day5 이동, 사전 예매 필수</t>
+        </is>
+      </c>
+      <c r="K12" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -3909,17 +3904,17 @@
       </c>
       <c r="B13" s="199" t="inlineStr">
         <is>
-          <t>구례→전주 버스</t>
+          <t>금오도 여객선 (왕복)</t>
         </is>
       </c>
       <c r="C13" s="198" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/12</t>
         </is>
       </c>
       <c r="D13" s="200" t="inlineStr">
         <is>
-          <t>고속버스 앱</t>
+          <t>여수연안여객터미널 현장</t>
         </is>
       </c>
       <c r="E13" s="200" t="inlineStr"/>
@@ -3927,7 +3922,7 @@
       <c r="G13" s="200" t="inlineStr"/>
       <c r="H13" s="199" t="inlineStr">
         <is>
-          <t>광복절 전날 혼잡</t>
+          <t>시간표 미리 확인</t>
         </is>
       </c>
       <c r="I13" s="198" t="inlineStr"/>
@@ -3946,12 +3941,12 @@
       </c>
       <c r="B14" s="199" t="inlineStr">
         <is>
-          <t>전주→단양 버스</t>
+          <t>구례→전주 버스</t>
         </is>
       </c>
       <c r="C14" s="198" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>8/14</t>
         </is>
       </c>
       <c r="D14" s="200" t="inlineStr">
@@ -3964,7 +3959,7 @@
       <c r="G14" s="200" t="inlineStr"/>
       <c r="H14" s="199" t="inlineStr">
         <is>
-          <t>청주 경유, 사전 예약</t>
+          <t>광복절 전날 혼잡</t>
         </is>
       </c>
       <c r="I14" s="198" t="inlineStr"/>
@@ -3983,12 +3978,12 @@
       </c>
       <c r="B15" s="199" t="inlineStr">
         <is>
-          <t>충주→서울 버스</t>
+          <t>전주→단양 버스</t>
         </is>
       </c>
       <c r="C15" s="198" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="D15" s="200" t="inlineStr">
@@ -4001,7 +3996,7 @@
       <c r="G15" s="200" t="inlineStr"/>
       <c r="H15" s="199" t="inlineStr">
         <is>
-          <t>마지막날 귀경</t>
+          <t>청주 경유, 사전 예약</t>
         </is>
       </c>
       <c r="I15" s="198" t="inlineStr"/>
@@ -4013,37 +4008,37 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="87">
-      <c r="A16" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B16" s="202" t="inlineStr">
-        <is>
-          <t>춘천 웨이크보드/모터보트</t>
-        </is>
-      </c>
-      <c r="C16" s="201" t="inlineStr">
-        <is>
-          <t>8/4</t>
-        </is>
-      </c>
-      <c r="D16" s="203" t="inlineStr">
-        <is>
-          <t>의암호 수상레저 전화/온라인</t>
-        </is>
-      </c>
-      <c r="E16" s="203" t="inlineStr"/>
-      <c r="F16" s="203" t="inlineStr"/>
-      <c r="G16" s="203" t="inlineStr"/>
-      <c r="H16" s="202" t="inlineStr">
-        <is>
-          <t>성수기 예약 권장</t>
-        </is>
-      </c>
-      <c r="I16" s="201" t="inlineStr"/>
-      <c r="J16" s="201" t="inlineStr"/>
-      <c r="K16" s="201" t="inlineStr">
+      <c r="A16" s="198" t="inlineStr">
+        <is>
+          <t>교통</t>
+        </is>
+      </c>
+      <c r="B16" s="199" t="inlineStr">
+        <is>
+          <t>단양→서울 버스</t>
+        </is>
+      </c>
+      <c r="C16" s="198" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+      <c r="D16" s="200" t="inlineStr">
+        <is>
+          <t>고속버스 앱</t>
+        </is>
+      </c>
+      <c r="E16" s="200" t="inlineStr"/>
+      <c r="F16" s="200" t="inlineStr"/>
+      <c r="G16" s="200" t="inlineStr"/>
+      <c r="H16" s="199" t="inlineStr">
+        <is>
+          <t>마지막날 귀경</t>
+        </is>
+      </c>
+      <c r="I16" s="198" t="inlineStr"/>
+      <c r="J16" s="198" t="inlineStr"/>
+      <c r="K16" s="198" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -4057,17 +4052,17 @@
       </c>
       <c r="B17" s="202" t="inlineStr">
         <is>
-          <t>블루라인파크 해변열차</t>
+          <t>춘천 웨이크보드/모터보트</t>
         </is>
       </c>
       <c r="C17" s="201" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>8/4</t>
         </is>
       </c>
       <c r="D17" s="203" t="inlineStr">
         <is>
-          <t>블루라인파크 홈페이지</t>
+          <t>의암호 수상레저 전화/온라인</t>
         </is>
       </c>
       <c r="E17" s="203" t="inlineStr"/>
@@ -4075,7 +4070,7 @@
       <c r="G17" s="203" t="inlineStr"/>
       <c r="H17" s="202" t="inlineStr">
         <is>
-          <t>예약 필수</t>
+          <t>성수기 예약 권장</t>
         </is>
       </c>
       <c r="I17" s="201" t="inlineStr"/>
@@ -4087,41 +4082,17 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" s="87">
-      <c r="A18" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B18" s="202" t="inlineStr">
-        <is>
-          <t>통영 케이블카</t>
-        </is>
-      </c>
-      <c r="C18" s="201" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
-      <c r="D18" s="203" t="inlineStr">
-        <is>
-          <t>현장 구매</t>
-        </is>
-      </c>
-      <c r="E18" s="203" t="inlineStr"/>
-      <c r="F18" s="203" t="inlineStr"/>
-      <c r="G18" s="203" t="inlineStr"/>
-      <c r="H18" s="202" t="inlineStr">
-        <is>
-          <t>성수기 대기 30분 예상</t>
-        </is>
-      </c>
-      <c r="I18" s="201" t="inlineStr"/>
-      <c r="J18" s="201" t="inlineStr"/>
-      <c r="K18" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
+      <c r="A18" s="201" t="n"/>
+      <c r="B18" s="202" t="n"/>
+      <c r="C18" s="201" t="n"/>
+      <c r="D18" s="203" t="n"/>
+      <c r="E18" s="203" t="n"/>
+      <c r="F18" s="203" t="n"/>
+      <c r="G18" s="203" t="n"/>
+      <c r="H18" s="202" t="n"/>
+      <c r="I18" s="201" t="n"/>
+      <c r="J18" s="201" t="n"/>
+      <c r="K18" s="201" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1" s="87">
       <c r="A19" s="201" t="inlineStr">
@@ -4131,17 +4102,17 @@
       </c>
       <c r="B19" s="202" t="inlineStr">
         <is>
-          <t>한일관 저녁</t>
+          <t>통영 케이블카</t>
         </is>
       </c>
       <c r="C19" s="201" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="D19" s="203" t="inlineStr">
         <is>
-          <t>전화 예약</t>
+          <t>현장 구매</t>
         </is>
       </c>
       <c r="E19" s="203" t="inlineStr"/>
@@ -4149,7 +4120,7 @@
       <c r="G19" s="203" t="inlineStr"/>
       <c r="H19" s="202" t="inlineStr">
         <is>
-          <t>⚠️ 반드시 사전 예약</t>
+          <t>성수기 대기 30분 예상</t>
         </is>
       </c>
       <c r="I19" s="201" t="inlineStr"/>
@@ -4168,12 +4139,12 @@
       </c>
       <c r="B20" s="202" t="inlineStr">
         <is>
-          <t>전주 한정식 점심</t>
+          <t>한일관 저녁</t>
         </is>
       </c>
       <c r="C20" s="201" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>8/11</t>
         </is>
       </c>
       <c r="D20" s="203" t="inlineStr">
@@ -4186,7 +4157,7 @@
       <c r="G20" s="203" t="inlineStr"/>
       <c r="H20" s="202" t="inlineStr">
         <is>
-          <t>인기 식당 사전 예약 필수</t>
+          <t>⚠️ 반드시 사전 예약</t>
         </is>
       </c>
       <c r="I20" s="201" t="inlineStr"/>
@@ -4205,7 +4176,7 @@
       </c>
       <c r="B21" s="202" t="inlineStr">
         <is>
-          <t>단양 래프팅</t>
+          <t>전주 한정식 점심</t>
         </is>
       </c>
       <c r="C21" s="201" t="inlineStr">
@@ -4215,7 +4186,7 @@
       </c>
       <c r="D21" s="203" t="inlineStr">
         <is>
-          <t>단양 래프팅 업체 전화/온라인</t>
+          <t>전화 예약</t>
         </is>
       </c>
       <c r="E21" s="203" t="inlineStr"/>
@@ -4223,7 +4194,7 @@
       <c r="G21" s="203" t="inlineStr"/>
       <c r="H21" s="202" t="inlineStr">
         <is>
-          <t>⚠️ 성수기 조기 마감</t>
+          <t>인기 식당 사전 예약 필수</t>
         </is>
       </c>
       <c r="I21" s="201" t="inlineStr"/>
@@ -4242,17 +4213,17 @@
       </c>
       <c r="B22" s="202" t="inlineStr">
         <is>
-          <t>단양 패러글라이딩</t>
+          <t>단양 래프팅</t>
         </is>
       </c>
       <c r="C22" s="201" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="D22" s="203" t="inlineStr">
         <is>
-          <t>양방산 패러글라이딩 전화</t>
+          <t>단양 래프팅 업체 전화/온라인</t>
         </is>
       </c>
       <c r="E22" s="203" t="inlineStr"/>
@@ -4260,7 +4231,7 @@
       <c r="G22" s="203" t="inlineStr"/>
       <c r="H22" s="202" t="inlineStr">
         <is>
-          <t>⚠️ 날씨 취소 가능</t>
+          <t>⚠️ 성수기 조기 마감</t>
         </is>
       </c>
       <c r="I22" s="201" t="inlineStr"/>
@@ -4279,7 +4250,7 @@
       </c>
       <c r="B23" s="202" t="inlineStr">
         <is>
-          <t>충주 활옥동굴</t>
+          <t>단양 패러글라이딩</t>
         </is>
       </c>
       <c r="C23" s="201" t="inlineStr">
@@ -4289,7 +4260,7 @@
       </c>
       <c r="D23" s="203" t="inlineStr">
         <is>
-          <t>현장 구매 가능</t>
+          <t>양방산 패러글라이딩 전화</t>
         </is>
       </c>
       <c r="E23" s="203" t="inlineStr"/>
@@ -4297,7 +4268,7 @@
       <c r="G23" s="203" t="inlineStr"/>
       <c r="H23" s="202" t="inlineStr">
         <is>
-          <t>내부 12°C — 겉옷 필수</t>
+          <t>⚠️ 날씨 취소 가능</t>
         </is>
       </c>
       <c r="I23" s="201" t="inlineStr"/>
@@ -4309,37 +4280,37 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" s="87">
-      <c r="A24" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B24" s="205" t="inlineStr">
-        <is>
-          <t>래쉬가드·수영복</t>
-        </is>
-      </c>
-      <c r="C24" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D24" s="206" t="inlineStr">
-        <is>
-          <t>구매</t>
-        </is>
-      </c>
-      <c r="E24" s="206" t="inlineStr"/>
-      <c r="F24" s="206" t="inlineStr"/>
-      <c r="G24" s="206" t="inlineStr"/>
-      <c r="H24" s="205" t="inlineStr">
-        <is>
-          <t>웨이크보드·래프팅 필수</t>
-        </is>
-      </c>
-      <c r="I24" s="204" t="inlineStr"/>
-      <c r="J24" s="204" t="inlineStr"/>
-      <c r="K24" s="204" t="inlineStr">
+      <c r="A24" s="201" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B24" s="202" t="inlineStr">
+        <is>
+          <t>충주 활옥동굴</t>
+        </is>
+      </c>
+      <c r="C24" s="201" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+      <c r="D24" s="203" t="inlineStr">
+        <is>
+          <t>현장 구매 가능</t>
+        </is>
+      </c>
+      <c r="E24" s="203" t="inlineStr"/>
+      <c r="F24" s="203" t="inlineStr"/>
+      <c r="G24" s="203" t="inlineStr"/>
+      <c r="H24" s="202" t="inlineStr">
+        <is>
+          <t>내부 12°C — 겉옷 필수</t>
+        </is>
+      </c>
+      <c r="I24" s="201" t="inlineStr"/>
+      <c r="J24" s="201" t="inlineStr"/>
+      <c r="K24" s="201" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -4353,7 +4324,7 @@
       </c>
       <c r="B25" s="205" t="inlineStr">
         <is>
-          <t>트레킹 장비 (등산화·스틱·우의)</t>
+          <t>래쉬가드·수영복</t>
         </is>
       </c>
       <c r="C25" s="204" t="inlineStr">
@@ -4363,7 +4334,7 @@
       </c>
       <c r="D25" s="206" t="inlineStr">
         <is>
-          <t>확인·구매</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="E25" s="206" t="inlineStr"/>
@@ -4371,7 +4342,7 @@
       <c r="G25" s="206" t="inlineStr"/>
       <c r="H25" s="205" t="inlineStr">
         <is>
-          <t>지리산 둘레길 필수</t>
+          <t>웨이크보드·래프팅 필수</t>
         </is>
       </c>
       <c r="I25" s="204" t="inlineStr"/>
@@ -4390,7 +4361,7 @@
       </c>
       <c r="B26" s="205" t="inlineStr">
         <is>
-          <t>방수팩</t>
+          <t>트레킹 장비 (등산화·스틱·우의)</t>
         </is>
       </c>
       <c r="C26" s="204" t="inlineStr">
@@ -4400,7 +4371,7 @@
       </c>
       <c r="D26" s="206" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>확인·구매</t>
         </is>
       </c>
       <c r="E26" s="206" t="inlineStr"/>
@@ -4408,7 +4379,7 @@
       <c r="G26" s="206" t="inlineStr"/>
       <c r="H26" s="205" t="inlineStr">
         <is>
-          <t>래프팅·수상레저 핸드폰 보호</t>
+          <t>지리산 둘레길 필수</t>
         </is>
       </c>
       <c r="I26" s="204" t="inlineStr"/>
@@ -4427,7 +4398,7 @@
       </c>
       <c r="B27" s="205" t="inlineStr">
         <is>
-          <t>여행자보험</t>
+          <t>방수팩</t>
         </is>
       </c>
       <c r="C27" s="204" t="inlineStr">
@@ -4437,7 +4408,7 @@
       </c>
       <c r="D27" s="206" t="inlineStr">
         <is>
-          <t>보험사 앱</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="E27" s="206" t="inlineStr"/>
@@ -4445,7 +4416,7 @@
       <c r="G27" s="206" t="inlineStr"/>
       <c r="H27" s="205" t="inlineStr">
         <is>
-          <t>액티비티 다수 — 필수</t>
+          <t>래프팅·수상레저 핸드폰 보호</t>
         </is>
       </c>
       <c r="I27" s="204" t="inlineStr"/>
@@ -4456,7 +4427,43 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="19.5" customHeight="1" s="87"/>
+    <row r="28" ht="19.5" customHeight="1" s="87">
+      <c r="A28" s="204" t="inlineStr">
+        <is>
+          <t>여행 준비</t>
+        </is>
+      </c>
+      <c r="B28" s="205" t="inlineStr">
+        <is>
+          <t>여행자보험</t>
+        </is>
+      </c>
+      <c r="C28" s="204" t="inlineStr">
+        <is>
+          <t>출발 전</t>
+        </is>
+      </c>
+      <c r="D28" s="206" t="inlineStr">
+        <is>
+          <t>보험사 앱</t>
+        </is>
+      </c>
+      <c r="E28" s="206" t="inlineStr"/>
+      <c r="F28" s="206" t="inlineStr"/>
+      <c r="G28" s="206" t="inlineStr"/>
+      <c r="H28" s="205" t="inlineStr">
+        <is>
+          <t>액티비티 다수 — 필수</t>
+        </is>
+      </c>
+      <c r="I28" s="204" t="inlineStr"/>
+      <c r="J28" s="204" t="inlineStr"/>
+      <c r="K28" s="204" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
     <row r="29" ht="19.5" customHeight="1" s="87"/>
     <row r="30" ht="19.5" customHeight="1" s="87"/>
     <row r="31" ht="19.5" customHeight="1" s="87"/>
@@ -5158,12 +5165,12 @@
       </c>
       <c r="B20" s="147" t="inlineStr">
         <is>
-          <t>아침</t>
+          <t>점심 (Day6)</t>
         </is>
       </c>
       <c r="C20" s="133" t="inlineStr">
         <is>
-          <t>쌍둥이돼지국밥</t>
+          <t>할매국밥 or 쌍둥이돼지국밥</t>
         </is>
       </c>
       <c r="D20" s="133" t="inlineStr">
@@ -5173,12 +5180,12 @@
       </c>
       <c r="E20" s="133" t="inlineStr">
         <is>
-          <t>부산 토박이 해장 1순위 서면 노포. 뽀얀 국물, 수육 한 접시. 아들도 부담 없이 OK</t>
+          <t>남포동 토박이 국밥골목. 뽀얀 육수에 수육 한 접시. 부산 와서 돼지국밥 안 먹으면 섭섭</t>
         </is>
       </c>
       <c r="F20" s="133" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면</t>
+          <t>부산 중구 남포동 비프광장 인근</t>
         </is>
       </c>
       <c r="G20" s="168" t="inlineStr">
@@ -5196,27 +5203,27 @@
       </c>
       <c r="B21" s="147" t="inlineStr">
         <is>
-          <t>점심</t>
+          <t>간식 (Day6)</t>
         </is>
       </c>
       <c r="C21" s="133" t="inlineStr">
         <is>
-          <t>초량 돼지갈비</t>
+          <t>씨앗호떡 (남포동)</t>
         </is>
       </c>
       <c r="D21" s="133" t="inlineStr">
         <is>
-          <t>돼지갈비·된장찌개 세트</t>
+          <t>씨앗호떡·납작만두</t>
         </is>
       </c>
       <c r="E21" s="133" t="inlineStr">
         <is>
-          <t>부산역 뒷골목 서민 밥상. 관광지 아닌 현지인 정식집. 두툼한 돼지갈비</t>
+          <t>★아들 픽★ BIFF광장 명물. 해바라기씨·땅콩 가득. 국제시장 납작만두도 필수</t>
         </is>
       </c>
       <c r="F21" s="133" t="inlineStr">
         <is>
-          <t>부산 동구 초량동</t>
+          <t>부산 중구 남포동 BIFF광장 일대</t>
         </is>
       </c>
       <c r="G21" s="168" t="inlineStr">
@@ -5234,27 +5241,27 @@
       </c>
       <c r="B22" s="147" t="inlineStr">
         <is>
-          <t>저녁</t>
+          <t>저녁 (Day6)</t>
         </is>
       </c>
       <c r="C22" s="133" t="inlineStr">
         <is>
-          <t>부전시장 빈대떡 골목</t>
+          <t>깡통시장 야시장</t>
         </is>
       </c>
       <c r="D22" s="133" t="inlineStr">
         <is>
-          <t>녹두빈대떡·돼지고기전·막걸리</t>
+          <t>비빔당면·납작만두·어묵탕</t>
         </is>
       </c>
       <c r="E22" s="133" t="inlineStr">
         <is>
-          <t>부산 전 명소. 부전시장 골목 빈대떡 노포들. 현지 어르신·직장인 저녁 단골 골목</t>
+          <t>미군 부대 통조림 시장 출신 야시장. 로컬 먹거리 집결. 18:00~자정 운영</t>
         </is>
       </c>
       <c r="F22" s="133" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전시장</t>
+          <t>부산 부산진구 부전시장 내</t>
         </is>
       </c>
       <c r="G22" s="168" t="inlineStr">
@@ -5266,32 +5273,33 @@
     <row r="23" ht="48" customHeight="1" s="87">
       <c r="A23" s="120" t="inlineStr">
         <is>
-          <t>통영</t>
+          <t>부산
+경남</t>
         </is>
       </c>
       <c r="B23" s="120" t="inlineStr">
         <is>
-          <t>점심</t>
+          <t>점심 (Day7)</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>강구식당</t>
+          <t>동래할매파전</t>
         </is>
       </c>
       <c r="D23" s="121" t="inlineStr">
         <is>
-          <t>미역국·전복구이 (구이)</t>
+          <t>동래파전·막걸리</t>
         </is>
       </c>
       <c r="E23" s="121" t="inlineStr">
         <is>
-          <t>통영 현지인 속 풀 때 찾는 미역국. 전복구이는 구운 것이라 아들도 OK</t>
+          <t>70년 전통 찹쌀 파전. 굴·새우·홍합 듬뿍. 11:30 전 도착 필수 (대기 심함)</t>
         </is>
       </c>
       <c r="F23" s="121" t="inlineStr">
         <is>
-          <t>경남 통영시 강구안</t>
+          <t>부산 동래구 동래시장로 57</t>
         </is>
       </c>
       <c r="G23" s="169" t="inlineStr">
@@ -5303,33 +5311,33 @@
     <row r="24" ht="48" customHeight="1" s="87">
       <c r="A24" s="120" t="inlineStr">
         <is>
-          <t>통영</t>
+          <t>부산
+경남</t>
         </is>
       </c>
       <c r="B24" s="120" t="inlineStr">
         <is>
-          <t>점심/저녁</t>
+          <t>저녁 (Day7)</t>
         </is>
       </c>
       <c r="C24" s="121" t="inlineStr">
         <is>
-          <t>통영 굴전·멸치쌈밥집
-(중앙시장 골목)</t>
+          <t>광안리 해산물 골목</t>
         </is>
       </c>
       <c r="D24" s="121" t="inlineStr">
         <is>
-          <t>굴전·멸치쌈밥·굴떡국</t>
+          <t>해산물·회·구이</t>
         </is>
       </c>
       <c r="E24" s="121" t="inlineStr">
         <is>
-          <t>통영 겨울 굴 철(8월은 어린 굴이지만 찜·전은 가능). 멸치쌈밥은 통영 현지 별미</t>
+          <t>광안대교 야경 보며 저녁. 민락수변공원 옆 해변 식당가. 현지인·관광객 공존</t>
         </is>
       </c>
       <c r="F24" s="121" t="inlineStr">
         <is>
-          <t>경남 통영시 중앙동</t>
+          <t>부산 수영구 광안해변로 일대</t>
         </is>
       </c>
       <c r="G24" s="169" t="inlineStr">
@@ -5916,42 +5924,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="86" t="inlineStr">
-        <is>
-          <t>부산
-경남</t>
-        </is>
-      </c>
-      <c r="B41" s="86" t="inlineStr">
-        <is>
-          <t>디저트/간식</t>
-        </is>
-      </c>
-      <c r="C41" s="86" t="inlineStr">
-        <is>
-          <t>씨앗호떡 (남포동)</t>
-        </is>
-      </c>
-      <c r="D41" s="86" t="inlineStr">
-        <is>
-          <t>씨앗호떡·꿀호떡</t>
-        </is>
-      </c>
-      <c r="E41" s="86" t="inlineStr">
-        <is>
-          <t>★아들 픽★ BIFF광장 골목 명물. 해바라기씨·땅콩 가득 바삭한 호떡. 줄 서서 먹는 맛</t>
-        </is>
-      </c>
-      <c r="F41" s="86" t="inlineStr">
-        <is>
-          <t>부산 중구 남포동 BIFF광장</t>
-        </is>
-      </c>
-      <c r="G41" s="86" t="inlineStr">
-        <is>
-          <t>📍 지도에서 보기</t>
-        </is>
-      </c>
+      <c r="A41" s="86" t="n"/>
+      <c r="B41" s="86" t="n"/>
+      <c r="C41" s="86" t="n"/>
+      <c r="D41" s="86" t="n"/>
+      <c r="E41" s="86" t="n"/>
+      <c r="F41" s="86" t="n"/>
+      <c r="G41" s="86" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="86" t="inlineStr">

--- a/2026_국토대장정_여행플래너.xlsx
+++ b/2026_국토대장정_여행플래너.xlsx
@@ -1742,6 +1742,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="9.75" customHeight="1" s="87"/>
     <row r="14" ht="19.5" customHeight="1" s="87">
       <c r="A14" s="98" t="inlineStr">
@@ -2262,301 +2263,223 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" s="87">
-      <c r="A10" s="173" t="inlineStr">
-        <is>
-          <t>Day 09</t>
-        </is>
-      </c>
-      <c r="B10" s="173" t="inlineStr">
-        <is>
-          <t>8/11</t>
-        </is>
-      </c>
-      <c r="C10" s="173" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="D10" s="173" t="inlineStr">
-        <is>
-          <t>통영</t>
-        </is>
-      </c>
-      <c r="E10" s="173" t="inlineStr">
+      <c r="A10" s="176" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B10" s="176" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="C10" s="176" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="D10" s="176" t="inlineStr">
         <is>
           <t>여수</t>
         </is>
       </c>
-      <c r="F10" s="174" t="inlineStr">
-        <is>
-          <t>최참판댁(토지) · 한일관 저녁 🍽️</t>
-        </is>
-      </c>
-      <c r="G10" s="173" t="inlineStr">
+      <c r="E10" s="176" t="inlineStr">
+        <is>
+          <t>여수</t>
+        </is>
+      </c>
+      <c r="F10" s="177" t="inlineStr">
+        <is>
+          <t>금오도 비렁길 트레킹 🥾</t>
+        </is>
+      </c>
+      <c r="G10" s="176" t="inlineStr">
         <is>
           <t>여수 부모님댁 🏠</t>
         </is>
       </c>
-      <c r="H10" s="175" t="n">
-        <v>136000</v>
+      <c r="H10" s="178" t="n">
+        <v>85000</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" s="87">
-      <c r="A11" s="176" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B11" s="176" t="inlineStr">
-        <is>
-          <t>8/12</t>
-        </is>
-      </c>
-      <c r="C11" s="176" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="D11" s="176" t="inlineStr">
+      <c r="A11" s="173" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B11" s="173" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+      <c r="C11" s="173" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="D11" s="173" t="inlineStr">
         <is>
           <t>여수</t>
         </is>
       </c>
-      <c r="E11" s="176" t="inlineStr">
-        <is>
-          <t>여수</t>
-        </is>
-      </c>
-      <c r="F11" s="177" t="inlineStr">
-        <is>
-          <t>금오도 비렁길 트레킹 🥾</t>
-        </is>
-      </c>
-      <c r="G11" s="176" t="inlineStr">
-        <is>
-          <t>여수 부모님댁 🏠</t>
-        </is>
-      </c>
-      <c r="H11" s="178" t="n">
-        <v>85000</v>
+      <c r="E11" s="173" t="inlineStr">
+        <is>
+          <t>지리산</t>
+        </is>
+      </c>
+      <c r="F11" s="174" t="inlineStr">
+        <is>
+          <t>지리산 둘레길 Day1 (평사리→의신마을)</t>
+        </is>
+      </c>
+      <c r="G11" s="173" t="inlineStr">
+        <is>
+          <t>의신마을 민박</t>
+        </is>
+      </c>
+      <c r="H11" s="175" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" s="87">
-      <c r="A12" s="173" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B12" s="173" t="inlineStr">
-        <is>
-          <t>8/13</t>
-        </is>
-      </c>
-      <c r="C12" s="173" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="D12" s="173" t="inlineStr">
-        <is>
-          <t>여수</t>
-        </is>
-      </c>
-      <c r="E12" s="173" t="inlineStr">
+      <c r="A12" s="176" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B12" s="176" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="C12" s="176" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="D12" s="176" t="inlineStr">
         <is>
           <t>지리산</t>
         </is>
       </c>
-      <c r="F12" s="174" t="inlineStr">
-        <is>
-          <t>지리산 둘레길 Day1 (평사리→의신마을)</t>
-        </is>
-      </c>
-      <c r="G12" s="173" t="inlineStr">
-        <is>
-          <t>의신마을 민박</t>
-        </is>
-      </c>
-      <c r="H12" s="175" t="n">
-        <v>120000</v>
+      <c r="E12" s="176" t="inlineStr">
+        <is>
+          <t>전주</t>
+        </is>
+      </c>
+      <c r="F12" s="177" t="inlineStr">
+        <is>
+          <t>지리산 둘레길 Day2 → 전주 이동</t>
+        </is>
+      </c>
+      <c r="G12" s="176" t="inlineStr">
+        <is>
+          <t>전주 한옥게스트하우스</t>
+        </is>
+      </c>
+      <c r="H12" s="178" t="n">
+        <v>83000</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" s="87">
-      <c r="A13" s="176" t="inlineStr">
-        <is>
-          <t>Day 12</t>
-        </is>
-      </c>
-      <c r="B13" s="176" t="inlineStr">
-        <is>
-          <t>8/14</t>
-        </is>
-      </c>
-      <c r="C13" s="176" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="D13" s="176" t="inlineStr">
-        <is>
-          <t>지리산</t>
-        </is>
-      </c>
-      <c r="E13" s="176" t="inlineStr">
+      <c r="A13" s="173" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B13" s="173" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="C13" s="173" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="D13" s="173" t="inlineStr">
         <is>
           <t>전주</t>
         </is>
       </c>
-      <c r="F13" s="177" t="inlineStr">
-        <is>
-          <t>지리산 둘레길 Day2 → 전주 이동</t>
-        </is>
-      </c>
-      <c r="G13" s="176" t="inlineStr">
-        <is>
-          <t>전주 한옥게스트하우스</t>
-        </is>
-      </c>
-      <c r="H13" s="178" t="n">
-        <v>83000</v>
+      <c r="E13" s="173" t="inlineStr">
+        <is>
+          <t>전주</t>
+        </is>
+      </c>
+      <c r="F13" s="174" t="inlineStr">
+        <is>
+          <t>광복절 🇰🇷 · 경기전 · 전주 막걸리골목</t>
+        </is>
+      </c>
+      <c r="G13" s="173" t="inlineStr">
+        <is>
+          <t>전주 연박</t>
+        </is>
+      </c>
+      <c r="H13" s="175" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" s="87">
-      <c r="A14" s="173" t="inlineStr">
-        <is>
-          <t>Day 13</t>
-        </is>
-      </c>
-      <c r="B14" s="173" t="inlineStr">
-        <is>
-          <t>8/15</t>
-        </is>
-      </c>
-      <c r="C14" s="173" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="D14" s="173" t="inlineStr">
+      <c r="A14" s="176" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B14" s="176" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+      <c r="C14" s="176" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="D14" s="176" t="inlineStr">
         <is>
           <t>전주</t>
         </is>
       </c>
-      <c r="E14" s="173" t="inlineStr">
-        <is>
-          <t>전주</t>
-        </is>
-      </c>
-      <c r="F14" s="174" t="inlineStr">
-        <is>
-          <t>광복절 🇰🇷 · 경기전 · 전주 막걸리골목</t>
-        </is>
-      </c>
-      <c r="G14" s="173" t="inlineStr">
-        <is>
-          <t>전주 연박</t>
-        </is>
-      </c>
-      <c r="H14" s="175" t="n">
-        <v>90000</v>
+      <c r="E14" s="176" t="inlineStr">
+        <is>
+          <t>단양</t>
+        </is>
+      </c>
+      <c r="F14" s="177" t="inlineStr">
+        <is>
+          <t>전주 한정식 🍱 · 단양 래프팅 🚣</t>
+        </is>
+      </c>
+      <c r="G14" s="176" t="inlineStr">
+        <is>
+          <t>단양 숙소</t>
+        </is>
+      </c>
+      <c r="H14" s="178" t="n">
+        <v>194000</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" s="87">
-      <c r="A15" s="176" t="inlineStr">
-        <is>
-          <t>Day 14</t>
-        </is>
-      </c>
-      <c r="B15" s="176" t="inlineStr">
-        <is>
-          <t>8/16</t>
-        </is>
-      </c>
-      <c r="C15" s="176" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="D15" s="176" t="inlineStr">
-        <is>
-          <t>전주</t>
-        </is>
-      </c>
-      <c r="E15" s="176" t="inlineStr">
-        <is>
-          <t>단양</t>
-        </is>
-      </c>
-      <c r="F15" s="177" t="inlineStr">
-        <is>
-          <t>전주 한정식 🍱 · 단양 래프팅 🚣</t>
-        </is>
-      </c>
-      <c r="G15" s="176" t="inlineStr">
-        <is>
-          <t>단양 숙소</t>
-        </is>
-      </c>
-      <c r="H15" s="178" t="n">
-        <v>194000</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" s="87">
-      <c r="A16" s="173" t="inlineStr">
-        <is>
-          <t>Day 15</t>
-        </is>
-      </c>
-      <c r="B16" s="173" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="C16" s="173" t="inlineStr">
-        <is>
-          <t>월</t>
-        </is>
-      </c>
-      <c r="D16" s="173" t="inlineStr">
-        <is>
-          <t>단양</t>
-        </is>
-      </c>
-      <c r="E16" s="173" t="inlineStr">
-        <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="F16" s="174" t="inlineStr">
-        <is>
-          <t>패러글라이딩 🪂 · 활옥동굴 · 귀경</t>
-        </is>
-      </c>
-      <c r="G16" s="173" t="inlineStr">
-        <is>
-          <t>집</t>
-        </is>
-      </c>
-      <c r="H16" s="175" t="n">
-        <v>257000</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="87">
-      <c r="A17" s="179" t="inlineStr">
+      <c r="A15" s="179" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B17" s="180" t="n"/>
-      <c r="C17" s="180" t="n"/>
-      <c r="D17" s="180" t="n"/>
-      <c r="E17" s="180" t="n"/>
-      <c r="F17" s="180" t="n"/>
-      <c r="G17" s="180" t="n"/>
-      <c r="H17" s="181" t="n">
+      <c r="B15" s="180" t="n"/>
+      <c r="C15" s="180" t="n"/>
+      <c r="D15" s="180" t="n"/>
+      <c r="E15" s="180" t="n"/>
+      <c r="F15" s="180" t="n"/>
+      <c r="G15" s="180" t="n"/>
+      <c r="H15" s="181" t="n">
         <v>1965400</v>
       </c>
     </row>
+    <row r="16" ht="28" customHeight="1" s="87"/>
+    <row r="17" ht="22" customHeight="1" s="87"/>
     <row r="18" ht="51.75" customHeight="1" s="87"/>
     <row r="19" ht="51.75" customHeight="1" s="87"/>
     <row r="20" ht="51.75" customHeight="1" s="87"/>
@@ -3427,6 +3350,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="21.75" customHeight="1" s="87">
       <c r="A36" s="98" t="inlineStr">
         <is>
@@ -3463,7 +3387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="86" min="1" max="1"/>
@@ -3724,17 +3648,17 @@
       </c>
       <c r="B8" s="196" t="inlineStr">
         <is>
-          <t>여수 부모님댁 (3박)</t>
+          <t>의신마을 민박</t>
         </is>
       </c>
       <c r="C8" s="195" t="inlineStr">
         <is>
-          <t>8/11~13</t>
+          <t>8/13~14</t>
         </is>
       </c>
       <c r="D8" s="197" t="inlineStr">
         <is>
-          <t>확정 🏠</t>
+          <t>전화 예약</t>
         </is>
       </c>
       <c r="E8" s="197" t="inlineStr"/>
@@ -3742,7 +3666,7 @@
       <c r="G8" s="197" t="inlineStr"/>
       <c r="H8" s="196" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>지리산 둘레길, 조기 마감 주의</t>
         </is>
       </c>
       <c r="I8" s="195" t="inlineStr"/>
@@ -3761,17 +3685,17 @@
       </c>
       <c r="B9" s="196" t="inlineStr">
         <is>
-          <t>의신마을 민박</t>
+          <t>전주 한옥 게스트하우스 (2박)</t>
         </is>
       </c>
       <c r="C9" s="195" t="inlineStr">
         <is>
-          <t>8/13~14</t>
+          <t>8/14~16</t>
         </is>
       </c>
       <c r="D9" s="197" t="inlineStr">
         <is>
-          <t>전화 예약</t>
+          <t>야놀자/여기어때</t>
         </is>
       </c>
       <c r="E9" s="197" t="inlineStr"/>
@@ -3779,7 +3703,7 @@
       <c r="G9" s="197" t="inlineStr"/>
       <c r="H9" s="196" t="inlineStr">
         <is>
-          <t>지리산 둘레길, 조기 마감 주의</t>
+          <t>한옥마을 내부</t>
         </is>
       </c>
       <c r="I9" s="195" t="inlineStr"/>
@@ -3798,12 +3722,12 @@
       </c>
       <c r="B10" s="196" t="inlineStr">
         <is>
-          <t>전주 한옥 게스트하우스 (2박)</t>
+          <t>단양 숙소</t>
         </is>
       </c>
       <c r="C10" s="195" t="inlineStr">
         <is>
-          <t>8/14~16</t>
+          <t>8/16~17</t>
         </is>
       </c>
       <c r="D10" s="197" t="inlineStr">
@@ -3816,7 +3740,7 @@
       <c r="G10" s="197" t="inlineStr"/>
       <c r="H10" s="196" t="inlineStr">
         <is>
-          <t>한옥마을 내부</t>
+          <t>래프팅 업체 근처</t>
         </is>
       </c>
       <c r="I10" s="195" t="inlineStr"/>
@@ -3828,69 +3752,69 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" s="87">
-      <c r="A11" s="195" t="inlineStr">
-        <is>
-          <t>숙박</t>
-        </is>
-      </c>
-      <c r="B11" s="196" t="inlineStr">
-        <is>
-          <t>단양 숙소</t>
-        </is>
-      </c>
-      <c r="C11" s="195" t="inlineStr">
-        <is>
-          <t>8/16~17</t>
-        </is>
-      </c>
-      <c r="D11" s="197" t="inlineStr">
-        <is>
-          <t>야놀자/여기어때</t>
-        </is>
-      </c>
-      <c r="E11" s="197" t="inlineStr"/>
-      <c r="F11" s="197" t="inlineStr"/>
-      <c r="G11" s="197" t="inlineStr"/>
-      <c r="H11" s="196" t="inlineStr">
-        <is>
-          <t>래프팅 업체 근처</t>
-        </is>
-      </c>
-      <c r="I11" s="195" t="inlineStr"/>
-      <c r="J11" s="195" t="inlineStr"/>
-      <c r="K11" s="195" t="inlineStr">
+      <c r="A11" s="86" t="inlineStr">
+        <is>
+          <t>교통</t>
+        </is>
+      </c>
+      <c r="B11" s="86" t="inlineStr">
+        <is>
+          <t>KTX 신경주→부산역</t>
+        </is>
+      </c>
+      <c r="C11" s="86" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="D11" s="86" t="inlineStr">
+        <is>
+          <t>korail.com or 코레일 앱</t>
+        </is>
+      </c>
+      <c r="H11" s="86" t="inlineStr">
+        <is>
+          <t>경주 Day5 이동, 사전 예매 필수</t>
+        </is>
+      </c>
+      <c r="K11" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="87">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="198" t="inlineStr">
         <is>
           <t>교통</t>
         </is>
       </c>
-      <c r="B12" s="86" t="inlineStr">
-        <is>
-          <t>KTX 신경주→부산역</t>
-        </is>
-      </c>
-      <c r="C12" s="86" t="inlineStr">
-        <is>
-          <t>8/8</t>
-        </is>
-      </c>
-      <c r="D12" s="86" t="inlineStr">
-        <is>
-          <t>korail.com or 코레일 앱</t>
-        </is>
-      </c>
-      <c r="H12" s="86" t="inlineStr">
-        <is>
-          <t>경주 Day5 이동, 사전 예매 필수</t>
-        </is>
-      </c>
-      <c r="K12" s="86" t="inlineStr">
+      <c r="B12" s="199" t="inlineStr">
+        <is>
+          <t>금오도 여객선 (왕복)</t>
+        </is>
+      </c>
+      <c r="C12" s="198" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="D12" s="200" t="inlineStr">
+        <is>
+          <t>여수연안여객터미널 현장</t>
+        </is>
+      </c>
+      <c r="E12" s="200" t="inlineStr"/>
+      <c r="F12" s="200" t="inlineStr"/>
+      <c r="G12" s="200" t="inlineStr"/>
+      <c r="H12" s="199" t="inlineStr">
+        <is>
+          <t>시간표 미리 확인</t>
+        </is>
+      </c>
+      <c r="I12" s="198" t="inlineStr"/>
+      <c r="J12" s="198" t="inlineStr"/>
+      <c r="K12" s="198" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -3904,17 +3828,17 @@
       </c>
       <c r="B13" s="199" t="inlineStr">
         <is>
-          <t>금오도 여객선 (왕복)</t>
+          <t>구례→전주 버스</t>
         </is>
       </c>
       <c r="C13" s="198" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>8/14</t>
         </is>
       </c>
       <c r="D13" s="200" t="inlineStr">
         <is>
-          <t>여수연안여객터미널 현장</t>
+          <t>고속버스 앱</t>
         </is>
       </c>
       <c r="E13" s="200" t="inlineStr"/>
@@ -3922,7 +3846,7 @@
       <c r="G13" s="200" t="inlineStr"/>
       <c r="H13" s="199" t="inlineStr">
         <is>
-          <t>시간표 미리 확인</t>
+          <t>광복절 전날 혼잡</t>
         </is>
       </c>
       <c r="I13" s="198" t="inlineStr"/>
@@ -3941,12 +3865,12 @@
       </c>
       <c r="B14" s="199" t="inlineStr">
         <is>
-          <t>구례→전주 버스</t>
+          <t>전주→단양 버스</t>
         </is>
       </c>
       <c r="C14" s="198" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="D14" s="200" t="inlineStr">
@@ -3959,7 +3883,7 @@
       <c r="G14" s="200" t="inlineStr"/>
       <c r="H14" s="199" t="inlineStr">
         <is>
-          <t>광복절 전날 혼잡</t>
+          <t>청주 경유, 사전 예약</t>
         </is>
       </c>
       <c r="I14" s="198" t="inlineStr"/>
@@ -3978,12 +3902,12 @@
       </c>
       <c r="B15" s="199" t="inlineStr">
         <is>
-          <t>전주→단양 버스</t>
+          <t>단양→서울 버스</t>
         </is>
       </c>
       <c r="C15" s="198" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>8/17</t>
         </is>
       </c>
       <c r="D15" s="200" t="inlineStr">
@@ -3996,7 +3920,7 @@
       <c r="G15" s="200" t="inlineStr"/>
       <c r="H15" s="199" t="inlineStr">
         <is>
-          <t>청주 경유, 사전 예약</t>
+          <t>마지막날 귀경</t>
         </is>
       </c>
       <c r="I15" s="198" t="inlineStr"/>
@@ -4008,91 +3932,91 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="87">
-      <c r="A16" s="198" t="inlineStr">
-        <is>
-          <t>교통</t>
-        </is>
-      </c>
-      <c r="B16" s="199" t="inlineStr">
-        <is>
-          <t>단양→서울 버스</t>
-        </is>
-      </c>
-      <c r="C16" s="198" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="D16" s="200" t="inlineStr">
-        <is>
-          <t>고속버스 앱</t>
-        </is>
-      </c>
-      <c r="E16" s="200" t="inlineStr"/>
-      <c r="F16" s="200" t="inlineStr"/>
-      <c r="G16" s="200" t="inlineStr"/>
-      <c r="H16" s="199" t="inlineStr">
-        <is>
-          <t>마지막날 귀경</t>
-        </is>
-      </c>
-      <c r="I16" s="198" t="inlineStr"/>
-      <c r="J16" s="198" t="inlineStr"/>
-      <c r="K16" s="198" t="inlineStr">
+      <c r="A16" s="201" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B16" s="202" t="inlineStr">
+        <is>
+          <t>춘천 웨이크보드/모터보트</t>
+        </is>
+      </c>
+      <c r="C16" s="201" t="inlineStr">
+        <is>
+          <t>8/4</t>
+        </is>
+      </c>
+      <c r="D16" s="203" t="inlineStr">
+        <is>
+          <t>의암호 수상레저 전화/온라인</t>
+        </is>
+      </c>
+      <c r="E16" s="203" t="inlineStr"/>
+      <c r="F16" s="203" t="inlineStr"/>
+      <c r="G16" s="203" t="inlineStr"/>
+      <c r="H16" s="202" t="inlineStr">
+        <is>
+          <t>성수기 예약 권장</t>
+        </is>
+      </c>
+      <c r="I16" s="201" t="inlineStr"/>
+      <c r="J16" s="201" t="inlineStr"/>
+      <c r="K16" s="201" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" s="87">
-      <c r="A17" s="201" t="inlineStr">
+      <c r="A17" s="201" t="n"/>
+      <c r="B17" s="202" t="n"/>
+      <c r="C17" s="201" t="n"/>
+      <c r="D17" s="203" t="n"/>
+      <c r="E17" s="203" t="n"/>
+      <c r="F17" s="203" t="n"/>
+      <c r="G17" s="203" t="n"/>
+      <c r="H17" s="202" t="n"/>
+      <c r="I17" s="201" t="n"/>
+      <c r="J17" s="201" t="n"/>
+      <c r="K17" s="201" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="87">
+      <c r="A18" s="201" t="inlineStr">
         <is>
           <t>체험</t>
         </is>
       </c>
-      <c r="B17" s="202" t="inlineStr">
-        <is>
-          <t>춘천 웨이크보드/모터보트</t>
-        </is>
-      </c>
-      <c r="C17" s="201" t="inlineStr">
-        <is>
-          <t>8/4</t>
-        </is>
-      </c>
-      <c r="D17" s="203" t="inlineStr">
-        <is>
-          <t>의암호 수상레저 전화/온라인</t>
-        </is>
-      </c>
-      <c r="E17" s="203" t="inlineStr"/>
-      <c r="F17" s="203" t="inlineStr"/>
-      <c r="G17" s="203" t="inlineStr"/>
-      <c r="H17" s="202" t="inlineStr">
-        <is>
-          <t>성수기 예약 권장</t>
-        </is>
-      </c>
-      <c r="I17" s="201" t="inlineStr"/>
-      <c r="J17" s="201" t="inlineStr"/>
-      <c r="K17" s="201" t="inlineStr">
+      <c r="B18" s="202" t="inlineStr">
+        <is>
+          <t>통영 케이블카</t>
+        </is>
+      </c>
+      <c r="C18" s="201" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D18" s="203" t="inlineStr">
+        <is>
+          <t>현장 구매</t>
+        </is>
+      </c>
+      <c r="E18" s="203" t="inlineStr"/>
+      <c r="F18" s="203" t="inlineStr"/>
+      <c r="G18" s="203" t="inlineStr"/>
+      <c r="H18" s="202" t="inlineStr">
+        <is>
+          <t>성수기 대기 30분 예상</t>
+        </is>
+      </c>
+      <c r="I18" s="201" t="inlineStr"/>
+      <c r="J18" s="201" t="inlineStr"/>
+      <c r="K18" s="201" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="87">
-      <c r="A18" s="201" t="n"/>
-      <c r="B18" s="202" t="n"/>
-      <c r="C18" s="201" t="n"/>
-      <c r="D18" s="203" t="n"/>
-      <c r="E18" s="203" t="n"/>
-      <c r="F18" s="203" t="n"/>
-      <c r="G18" s="203" t="n"/>
-      <c r="H18" s="202" t="n"/>
-      <c r="I18" s="201" t="n"/>
-      <c r="J18" s="201" t="n"/>
-      <c r="K18" s="201" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1" s="87">
       <c r="A19" s="201" t="inlineStr">
@@ -4102,17 +4026,17 @@
       </c>
       <c r="B19" s="202" t="inlineStr">
         <is>
-          <t>통영 케이블카</t>
+          <t>한일관 저녁</t>
         </is>
       </c>
       <c r="C19" s="201" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>8/11</t>
         </is>
       </c>
       <c r="D19" s="203" t="inlineStr">
         <is>
-          <t>현장 구매</t>
+          <t>전화 예약</t>
         </is>
       </c>
       <c r="E19" s="203" t="inlineStr"/>
@@ -4120,7 +4044,7 @@
       <c r="G19" s="203" t="inlineStr"/>
       <c r="H19" s="202" t="inlineStr">
         <is>
-          <t>성수기 대기 30분 예상</t>
+          <t>⚠️ 반드시 사전 예약</t>
         </is>
       </c>
       <c r="I19" s="201" t="inlineStr"/>
@@ -4139,12 +4063,12 @@
       </c>
       <c r="B20" s="202" t="inlineStr">
         <is>
-          <t>한일관 저녁</t>
+          <t>전주 한정식 점심</t>
         </is>
       </c>
       <c r="C20" s="201" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="D20" s="203" t="inlineStr">
@@ -4157,7 +4081,7 @@
       <c r="G20" s="203" t="inlineStr"/>
       <c r="H20" s="202" t="inlineStr">
         <is>
-          <t>⚠️ 반드시 사전 예약</t>
+          <t>인기 식당 사전 예약 필수</t>
         </is>
       </c>
       <c r="I20" s="201" t="inlineStr"/>
@@ -4176,7 +4100,7 @@
       </c>
       <c r="B21" s="202" t="inlineStr">
         <is>
-          <t>전주 한정식 점심</t>
+          <t>단양 래프팅</t>
         </is>
       </c>
       <c r="C21" s="201" t="inlineStr">
@@ -4186,7 +4110,7 @@
       </c>
       <c r="D21" s="203" t="inlineStr">
         <is>
-          <t>전화 예약</t>
+          <t>단양 래프팅 업체 전화/온라인</t>
         </is>
       </c>
       <c r="E21" s="203" t="inlineStr"/>
@@ -4194,7 +4118,7 @@
       <c r="G21" s="203" t="inlineStr"/>
       <c r="H21" s="202" t="inlineStr">
         <is>
-          <t>인기 식당 사전 예약 필수</t>
+          <t>⚠️ 성수기 조기 마감</t>
         </is>
       </c>
       <c r="I21" s="201" t="inlineStr"/>
@@ -4213,17 +4137,17 @@
       </c>
       <c r="B22" s="202" t="inlineStr">
         <is>
-          <t>단양 래프팅</t>
+          <t>충주 활옥동굴</t>
         </is>
       </c>
       <c r="C22" s="201" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>8/17</t>
         </is>
       </c>
       <c r="D22" s="203" t="inlineStr">
         <is>
-          <t>단양 래프팅 업체 전화/온라인</t>
+          <t>현장 구매 가능</t>
         </is>
       </c>
       <c r="E22" s="203" t="inlineStr"/>
@@ -4231,7 +4155,7 @@
       <c r="G22" s="203" t="inlineStr"/>
       <c r="H22" s="202" t="inlineStr">
         <is>
-          <t>⚠️ 성수기 조기 마감</t>
+          <t>내부 12°C — 겉옷 필수</t>
         </is>
       </c>
       <c r="I22" s="201" t="inlineStr"/>
@@ -4243,74 +4167,74 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" s="87">
-      <c r="A23" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B23" s="202" t="inlineStr">
-        <is>
-          <t>단양 패러글라이딩</t>
-        </is>
-      </c>
-      <c r="C23" s="201" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="D23" s="203" t="inlineStr">
-        <is>
-          <t>양방산 패러글라이딩 전화</t>
-        </is>
-      </c>
-      <c r="E23" s="203" t="inlineStr"/>
-      <c r="F23" s="203" t="inlineStr"/>
-      <c r="G23" s="203" t="inlineStr"/>
-      <c r="H23" s="202" t="inlineStr">
-        <is>
-          <t>⚠️ 날씨 취소 가능</t>
-        </is>
-      </c>
-      <c r="I23" s="201" t="inlineStr"/>
-      <c r="J23" s="201" t="inlineStr"/>
-      <c r="K23" s="201" t="inlineStr">
+      <c r="A23" s="204" t="inlineStr">
+        <is>
+          <t>여행 준비</t>
+        </is>
+      </c>
+      <c r="B23" s="205" t="inlineStr">
+        <is>
+          <t>래쉬가드·수영복</t>
+        </is>
+      </c>
+      <c r="C23" s="204" t="inlineStr">
+        <is>
+          <t>출발 전</t>
+        </is>
+      </c>
+      <c r="D23" s="206" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="E23" s="206" t="inlineStr"/>
+      <c r="F23" s="206" t="inlineStr"/>
+      <c r="G23" s="206" t="inlineStr"/>
+      <c r="H23" s="205" t="inlineStr">
+        <is>
+          <t>웨이크보드·래프팅 필수</t>
+        </is>
+      </c>
+      <c r="I23" s="204" t="inlineStr"/>
+      <c r="J23" s="204" t="inlineStr"/>
+      <c r="K23" s="204" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" s="87">
-      <c r="A24" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B24" s="202" t="inlineStr">
-        <is>
-          <t>충주 활옥동굴</t>
-        </is>
-      </c>
-      <c r="C24" s="201" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="D24" s="203" t="inlineStr">
-        <is>
-          <t>현장 구매 가능</t>
-        </is>
-      </c>
-      <c r="E24" s="203" t="inlineStr"/>
-      <c r="F24" s="203" t="inlineStr"/>
-      <c r="G24" s="203" t="inlineStr"/>
-      <c r="H24" s="202" t="inlineStr">
-        <is>
-          <t>내부 12°C — 겉옷 필수</t>
-        </is>
-      </c>
-      <c r="I24" s="201" t="inlineStr"/>
-      <c r="J24" s="201" t="inlineStr"/>
-      <c r="K24" s="201" t="inlineStr">
+      <c r="A24" s="204" t="inlineStr">
+        <is>
+          <t>여행 준비</t>
+        </is>
+      </c>
+      <c r="B24" s="205" t="inlineStr">
+        <is>
+          <t>트레킹 장비 (등산화·스틱·우의)</t>
+        </is>
+      </c>
+      <c r="C24" s="204" t="inlineStr">
+        <is>
+          <t>출발 전</t>
+        </is>
+      </c>
+      <c r="D24" s="206" t="inlineStr">
+        <is>
+          <t>확인·구매</t>
+        </is>
+      </c>
+      <c r="E24" s="206" t="inlineStr"/>
+      <c r="F24" s="206" t="inlineStr"/>
+      <c r="G24" s="206" t="inlineStr"/>
+      <c r="H24" s="205" t="inlineStr">
+        <is>
+          <t>지리산 둘레길 필수</t>
+        </is>
+      </c>
+      <c r="I24" s="204" t="inlineStr"/>
+      <c r="J24" s="204" t="inlineStr"/>
+      <c r="K24" s="204" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -4324,7 +4248,7 @@
       </c>
       <c r="B25" s="205" t="inlineStr">
         <is>
-          <t>래쉬가드·수영복</t>
+          <t>방수팩</t>
         </is>
       </c>
       <c r="C25" s="204" t="inlineStr">
@@ -4342,7 +4266,7 @@
       <c r="G25" s="206" t="inlineStr"/>
       <c r="H25" s="205" t="inlineStr">
         <is>
-          <t>웨이크보드·래프팅 필수</t>
+          <t>래프팅·수상레저 핸드폰 보호</t>
         </is>
       </c>
       <c r="I25" s="204" t="inlineStr"/>
@@ -4361,7 +4285,7 @@
       </c>
       <c r="B26" s="205" t="inlineStr">
         <is>
-          <t>트레킹 장비 (등산화·스틱·우의)</t>
+          <t>여행자보험</t>
         </is>
       </c>
       <c r="C26" s="204" t="inlineStr">
@@ -4371,7 +4295,7 @@
       </c>
       <c r="D26" s="206" t="inlineStr">
         <is>
-          <t>확인·구매</t>
+          <t>보험사 앱</t>
         </is>
       </c>
       <c r="E26" s="206" t="inlineStr"/>
@@ -4379,7 +4303,7 @@
       <c r="G26" s="206" t="inlineStr"/>
       <c r="H26" s="205" t="inlineStr">
         <is>
-          <t>지리산 둘레길 필수</t>
+          <t>액티비티 다수 — 필수</t>
         </is>
       </c>
       <c r="I26" s="204" t="inlineStr"/>
@@ -4390,80 +4314,8 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1" s="87">
-      <c r="A27" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B27" s="205" t="inlineStr">
-        <is>
-          <t>방수팩</t>
-        </is>
-      </c>
-      <c r="C27" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D27" s="206" t="inlineStr">
-        <is>
-          <t>구매</t>
-        </is>
-      </c>
-      <c r="E27" s="206" t="inlineStr"/>
-      <c r="F27" s="206" t="inlineStr"/>
-      <c r="G27" s="206" t="inlineStr"/>
-      <c r="H27" s="205" t="inlineStr">
-        <is>
-          <t>래프팅·수상레저 핸드폰 보호</t>
-        </is>
-      </c>
-      <c r="I27" s="204" t="inlineStr"/>
-      <c r="J27" s="204" t="inlineStr"/>
-      <c r="K27" s="204" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1" s="87">
-      <c r="A28" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B28" s="205" t="inlineStr">
-        <is>
-          <t>여행자보험</t>
-        </is>
-      </c>
-      <c r="C28" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D28" s="206" t="inlineStr">
-        <is>
-          <t>보험사 앱</t>
-        </is>
-      </c>
-      <c r="E28" s="206" t="inlineStr"/>
-      <c r="F28" s="206" t="inlineStr"/>
-      <c r="G28" s="206" t="inlineStr"/>
-      <c r="H28" s="205" t="inlineStr">
-        <is>
-          <t>액티비티 다수 — 필수</t>
-        </is>
-      </c>
-      <c r="I28" s="204" t="inlineStr"/>
-      <c r="J28" s="204" t="inlineStr"/>
-      <c r="K28" s="204" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
+    <row r="27" ht="22" customHeight="1" s="87"/>
+    <row r="28" ht="19.5" customHeight="1" s="87"/>
     <row r="29" ht="19.5" customHeight="1" s="87"/>
     <row r="30" ht="19.5" customHeight="1" s="87"/>
     <row r="31" ht="19.5" customHeight="1" s="87"/>

--- a/2026_국토대장정_여행플래너.xlsx
+++ b/2026_국토대장정_여행플래너.xlsx
@@ -1742,7 +1742,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="9.75" customHeight="1" s="87"/>
     <row r="14" ht="19.5" customHeight="1" s="87">
       <c r="A14" s="98" t="inlineStr">
@@ -1911,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="86" min="1" max="1"/>
@@ -2305,179 +2304,101 @@
     <row r="11" ht="28" customHeight="1" s="87">
       <c r="A11" s="173" t="inlineStr">
         <is>
-          <t>Day 11</t>
+          <t>Day 13</t>
         </is>
       </c>
       <c r="B11" s="173" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>8/15</t>
         </is>
       </c>
       <c r="C11" s="173" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D11" s="173" t="inlineStr">
         <is>
-          <t>여수</t>
+          <t>전주</t>
         </is>
       </c>
       <c r="E11" s="173" t="inlineStr">
         <is>
-          <t>지리산</t>
+          <t>전주</t>
         </is>
       </c>
       <c r="F11" s="174" t="inlineStr">
         <is>
-          <t>지리산 둘레길 Day1 (평사리→의신마을)</t>
+          <t>광복절 🇰🇷 · 경기전 · 전주 막걸리골목</t>
         </is>
       </c>
       <c r="G11" s="173" t="inlineStr">
         <is>
-          <t>의신마을 민박</t>
+          <t>전주 연박</t>
         </is>
       </c>
       <c r="H11" s="175" t="n">
-        <v>120000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" s="87">
       <c r="A12" s="176" t="inlineStr">
         <is>
-          <t>Day 12</t>
+          <t>Day 14</t>
         </is>
       </c>
       <c r="B12" s="176" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/16</t>
         </is>
       </c>
       <c r="C12" s="176" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D12" s="176" t="inlineStr">
         <is>
-          <t>지리산</t>
+          <t>전주</t>
         </is>
       </c>
       <c r="E12" s="176" t="inlineStr">
         <is>
-          <t>전주</t>
+          <t>단양</t>
         </is>
       </c>
       <c r="F12" s="177" t="inlineStr">
         <is>
-          <t>지리산 둘레길 Day2 → 전주 이동</t>
+          <t>전주 한정식 🍱 · 단양 래프팅 🚣</t>
         </is>
       </c>
       <c r="G12" s="176" t="inlineStr">
         <is>
-          <t>전주 한옥게스트하우스</t>
+          <t>단양 숙소</t>
         </is>
       </c>
       <c r="H12" s="178" t="n">
-        <v>83000</v>
+        <v>194000</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" s="87">
-      <c r="A13" s="173" t="inlineStr">
-        <is>
-          <t>Day 13</t>
-        </is>
-      </c>
-      <c r="B13" s="173" t="inlineStr">
-        <is>
-          <t>8/15</t>
-        </is>
-      </c>
-      <c r="C13" s="173" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="D13" s="173" t="inlineStr">
-        <is>
-          <t>전주</t>
-        </is>
-      </c>
-      <c r="E13" s="173" t="inlineStr">
-        <is>
-          <t>전주</t>
-        </is>
-      </c>
-      <c r="F13" s="174" t="inlineStr">
-        <is>
-          <t>광복절 🇰🇷 · 경기전 · 전주 막걸리골목</t>
-        </is>
-      </c>
-      <c r="G13" s="173" t="inlineStr">
-        <is>
-          <t>전주 연박</t>
-        </is>
-      </c>
-      <c r="H13" s="175" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" s="87">
-      <c r="A14" s="176" t="inlineStr">
-        <is>
-          <t>Day 14</t>
-        </is>
-      </c>
-      <c r="B14" s="176" t="inlineStr">
-        <is>
-          <t>8/16</t>
-        </is>
-      </c>
-      <c r="C14" s="176" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="D14" s="176" t="inlineStr">
-        <is>
-          <t>전주</t>
-        </is>
-      </c>
-      <c r="E14" s="176" t="inlineStr">
-        <is>
-          <t>단양</t>
-        </is>
-      </c>
-      <c r="F14" s="177" t="inlineStr">
-        <is>
-          <t>전주 한정식 🍱 · 단양 래프팅 🚣</t>
-        </is>
-      </c>
-      <c r="G14" s="176" t="inlineStr">
-        <is>
-          <t>단양 숙소</t>
-        </is>
-      </c>
-      <c r="H14" s="178" t="n">
-        <v>194000</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" s="87">
-      <c r="A15" s="179" t="inlineStr">
+      <c r="A13" s="179" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B15" s="180" t="n"/>
-      <c r="C15" s="180" t="n"/>
-      <c r="D15" s="180" t="n"/>
-      <c r="E15" s="180" t="n"/>
-      <c r="F15" s="180" t="n"/>
-      <c r="G15" s="180" t="n"/>
-      <c r="H15" s="181" t="n">
+      <c r="B13" s="180" t="n"/>
+      <c r="C13" s="180" t="n"/>
+      <c r="D13" s="180" t="n"/>
+      <c r="E13" s="180" t="n"/>
+      <c r="F13" s="180" t="n"/>
+      <c r="G13" s="180" t="n"/>
+      <c r="H13" s="181" t="n">
         <v>1965400</v>
       </c>
     </row>
+    <row r="14" ht="28" customHeight="1" s="87"/>
+    <row r="15" ht="28" customHeight="1" s="87"/>
     <row r="16" ht="28" customHeight="1" s="87"/>
     <row r="17" ht="22" customHeight="1" s="87"/>
     <row r="18" ht="51.75" customHeight="1" s="87"/>
@@ -2487,6 +2408,40 @@
     <row r="22" ht="51.75" customHeight="1" s="87"/>
     <row r="23" ht="51.75" customHeight="1" s="87"/>
     <row r="24" ht="19.5" customHeight="1" s="87"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8/13(목)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>안도 해수욕장 🌊 + 여수밤바다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8/14(금)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>순천만 국가정원 🌿 → 전주 이동</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -3350,7 +3305,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="21.75" customHeight="1" s="87">
       <c r="A36" s="98" t="inlineStr">
         <is>
@@ -3387,7 +3341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="86" min="1" max="1"/>
@@ -3648,17 +3602,17 @@
       </c>
       <c r="B8" s="196" t="inlineStr">
         <is>
-          <t>의신마을 민박</t>
+          <t>전주 한옥 게스트하우스 (2박)</t>
         </is>
       </c>
       <c r="C8" s="195" t="inlineStr">
         <is>
-          <t>8/13~14</t>
+          <t>8/14~16</t>
         </is>
       </c>
       <c r="D8" s="197" t="inlineStr">
         <is>
-          <t>전화 예약</t>
+          <t>야놀자/여기어때</t>
         </is>
       </c>
       <c r="E8" s="197" t="inlineStr"/>
@@ -3666,7 +3620,7 @@
       <c r="G8" s="197" t="inlineStr"/>
       <c r="H8" s="196" t="inlineStr">
         <is>
-          <t>지리산 둘레길, 조기 마감 주의</t>
+          <t>한옥마을 내부</t>
         </is>
       </c>
       <c r="I8" s="195" t="inlineStr"/>
@@ -3685,12 +3639,12 @@
       </c>
       <c r="B9" s="196" t="inlineStr">
         <is>
-          <t>전주 한옥 게스트하우스 (2박)</t>
+          <t>단양 숙소</t>
         </is>
       </c>
       <c r="C9" s="195" t="inlineStr">
         <is>
-          <t>8/14~16</t>
+          <t>8/16~17</t>
         </is>
       </c>
       <c r="D9" s="197" t="inlineStr">
@@ -3703,7 +3657,7 @@
       <c r="G9" s="197" t="inlineStr"/>
       <c r="H9" s="196" t="inlineStr">
         <is>
-          <t>한옥마을 내부</t>
+          <t>래프팅 업체 근처</t>
         </is>
       </c>
       <c r="I9" s="195" t="inlineStr"/>
@@ -3715,108 +3669,93 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" s="87">
-      <c r="A10" s="195" t="inlineStr">
-        <is>
-          <t>숙박</t>
-        </is>
-      </c>
-      <c r="B10" s="196" t="inlineStr">
-        <is>
-          <t>단양 숙소</t>
-        </is>
-      </c>
-      <c r="C10" s="195" t="inlineStr">
-        <is>
-          <t>8/16~17</t>
-        </is>
-      </c>
-      <c r="D10" s="197" t="inlineStr">
-        <is>
-          <t>야놀자/여기어때</t>
-        </is>
-      </c>
-      <c r="E10" s="197" t="inlineStr"/>
-      <c r="F10" s="197" t="inlineStr"/>
-      <c r="G10" s="197" t="inlineStr"/>
-      <c r="H10" s="196" t="inlineStr">
-        <is>
-          <t>래프팅 업체 근처</t>
-        </is>
-      </c>
-      <c r="I10" s="195" t="inlineStr"/>
-      <c r="J10" s="195" t="inlineStr"/>
-      <c r="K10" s="195" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
+        <is>
+          <t>교통</t>
+        </is>
+      </c>
+      <c r="B10" s="86" t="inlineStr">
+        <is>
+          <t>KTX 신경주→부산역</t>
+        </is>
+      </c>
+      <c r="C10" s="86" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="D10" s="86" t="inlineStr">
+        <is>
+          <t>korail.com or 코레일 앱</t>
+        </is>
+      </c>
+      <c r="H10" s="86" t="inlineStr">
+        <is>
+          <t>경주 Day5 이동, 사전 예매 필수</t>
+        </is>
+      </c>
+      <c r="K10" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" s="87">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="198" t="inlineStr">
         <is>
           <t>교통</t>
         </is>
       </c>
-      <c r="B11" s="86" t="inlineStr">
-        <is>
-          <t>KTX 신경주→부산역</t>
-        </is>
-      </c>
-      <c r="C11" s="86" t="inlineStr">
-        <is>
-          <t>8/8</t>
-        </is>
-      </c>
-      <c r="D11" s="86" t="inlineStr">
-        <is>
-          <t>korail.com or 코레일 앱</t>
-        </is>
-      </c>
-      <c r="H11" s="86" t="inlineStr">
-        <is>
-          <t>경주 Day5 이동, 사전 예매 필수</t>
-        </is>
-      </c>
-      <c r="K11" s="86" t="inlineStr">
+      <c r="B11" s="199" t="inlineStr">
+        <is>
+          <t>금오도 여객선 (왕복)</t>
+        </is>
+      </c>
+      <c r="C11" s="198" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="D11" s="200" t="inlineStr">
+        <is>
+          <t>여수연안여객터미널 현장</t>
+        </is>
+      </c>
+      <c r="E11" s="200" t="inlineStr"/>
+      <c r="F11" s="200" t="inlineStr"/>
+      <c r="G11" s="200" t="inlineStr"/>
+      <c r="H11" s="199" t="inlineStr">
+        <is>
+          <t>시간표 미리 확인</t>
+        </is>
+      </c>
+      <c r="I11" s="198" t="inlineStr"/>
+      <c r="J11" s="198" t="inlineStr"/>
+      <c r="K11" s="198" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="87">
-      <c r="A12" s="198" t="inlineStr">
-        <is>
-          <t>교통</t>
-        </is>
-      </c>
-      <c r="B12" s="199" t="inlineStr">
-        <is>
-          <t>금오도 여객선 (왕복)</t>
-        </is>
-      </c>
-      <c r="C12" s="198" t="inlineStr">
-        <is>
-          <t>8/12</t>
-        </is>
-      </c>
-      <c r="D12" s="200" t="inlineStr">
-        <is>
-          <t>여수연안여객터미널 현장</t>
-        </is>
-      </c>
-      <c r="E12" s="200" t="inlineStr"/>
-      <c r="F12" s="200" t="inlineStr"/>
-      <c r="G12" s="200" t="inlineStr"/>
-      <c r="H12" s="199" t="inlineStr">
-        <is>
-          <t>시간표 미리 확인</t>
-        </is>
-      </c>
-      <c r="I12" s="198" t="inlineStr"/>
-      <c r="J12" s="198" t="inlineStr"/>
-      <c r="K12" s="198" t="inlineStr">
-        <is>
-          <t>☐</t>
+      <c r="A12" s="86" t="inlineStr">
+        <is>
+          <t>포시즌펜션 (금오도)</t>
+        </is>
+      </c>
+      <c r="B12" s="86" t="inlineStr">
+        <is>
+          <t>8/12~13</t>
+        </is>
+      </c>
+      <c r="C12" s="86" t="inlineStr">
+        <is>
+          <t>숙소</t>
+        </is>
+      </c>
+      <c r="D12" s="86" t="inlineStr">
+        <is>
+          <t>전화 예약 필수</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4150,7 @@
       </c>
       <c r="B24" s="205" t="inlineStr">
         <is>
-          <t>트레킹 장비 (등산화·스틱·우의)</t>
+          <t>방수팩</t>
         </is>
       </c>
       <c r="C24" s="204" t="inlineStr">
@@ -4221,7 +4160,7 @@
       </c>
       <c r="D24" s="206" t="inlineStr">
         <is>
-          <t>확인·구매</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="E24" s="206" t="inlineStr"/>
@@ -4229,7 +4168,7 @@
       <c r="G24" s="206" t="inlineStr"/>
       <c r="H24" s="205" t="inlineStr">
         <is>
-          <t>지리산 둘레길 필수</t>
+          <t>래프팅·수상레저 핸드폰 보호</t>
         </is>
       </c>
       <c r="I24" s="204" t="inlineStr"/>
@@ -4248,7 +4187,7 @@
       </c>
       <c r="B25" s="205" t="inlineStr">
         <is>
-          <t>방수팩</t>
+          <t>여행자보험</t>
         </is>
       </c>
       <c r="C25" s="204" t="inlineStr">
@@ -4258,7 +4197,7 @@
       </c>
       <c r="D25" s="206" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>보험사 앱</t>
         </is>
       </c>
       <c r="E25" s="206" t="inlineStr"/>
@@ -4266,7 +4205,7 @@
       <c r="G25" s="206" t="inlineStr"/>
       <c r="H25" s="205" t="inlineStr">
         <is>
-          <t>래프팅·수상레저 핸드폰 보호</t>
+          <t>액티비티 다수 — 필수</t>
         </is>
       </c>
       <c r="I25" s="204" t="inlineStr"/>
@@ -4277,43 +4216,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1" s="87">
-      <c r="A26" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B26" s="205" t="inlineStr">
-        <is>
-          <t>여행자보험</t>
-        </is>
-      </c>
-      <c r="C26" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D26" s="206" t="inlineStr">
-        <is>
-          <t>보험사 앱</t>
-        </is>
-      </c>
-      <c r="E26" s="206" t="inlineStr"/>
-      <c r="F26" s="206" t="inlineStr"/>
-      <c r="G26" s="206" t="inlineStr"/>
-      <c r="H26" s="205" t="inlineStr">
-        <is>
-          <t>액티비티 다수 — 필수</t>
-        </is>
-      </c>
-      <c r="I26" s="204" t="inlineStr"/>
-      <c r="J26" s="204" t="inlineStr"/>
-      <c r="K26" s="204" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
+    <row r="26" ht="22" customHeight="1" s="87"/>
     <row r="27" ht="22" customHeight="1" s="87"/>
     <row r="28" ht="19.5" customHeight="1" s="87"/>
     <row r="29" ht="19.5" customHeight="1" s="87"/>

--- a/2026_국토대장정_여행플래너.xlsx
+++ b/2026_국토대장정_여행플래너.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -229,8 +229,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="DejaVu Sans"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF1155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -391,6 +401,24 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAE8FC"/>
+        <bgColor rgb="FFDAE8FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -497,7 +525,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1104,6 +1132,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2409,37 +2455,60 @@
     <row r="23" ht="51.75" customHeight="1" s="87"/>
     <row r="24" ht="19.5" customHeight="1" s="87"/>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="86" t="inlineStr">
         <is>
           <t>8/13(목)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="86" t="inlineStr">
         <is>
           <t>안도 해수욕장 🌊 + 여수밤바다</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="86" t="inlineStr">
         <is>
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>8/14(금)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>순천만 국가정원 🌿 → 전주 이동</t>
-        </is>
+      <c r="B26" s="86" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="C26" s="86" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="D26" s="86" t="inlineStr">
+        <is>
+          <t>여수</t>
+        </is>
+      </c>
+      <c r="E26" s="86" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="F26" s="86" t="inlineStr">
+        <is>
+          <t>담양 소쇄원 🌿 + 광주 5·18 역사 🏛️</t>
+        </is>
+      </c>
+      <c r="G26" s="86" t="inlineStr">
+        <is>
+          <t>광주 숙소</t>
+        </is>
+      </c>
+      <c r="H26" s="86" t="n">
+        <v>156000</v>
       </c>
     </row>
   </sheetData>
@@ -3341,7 +3410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="86" min="1" max="1"/>
@@ -3363,6 +3432,11 @@
           <t>2026 국토대장정 — 예약 체크리스트</t>
         </is>
       </c>
+      <c r="L1" s="86" t="inlineStr">
+        <is>
+          <t>stable_id</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="87">
       <c r="A2" s="194" t="inlineStr">
@@ -3410,812 +3484,759 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" s="87">
-      <c r="A3" s="195" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>숙박</t>
         </is>
       </c>
-      <c r="B3" s="196" t="inlineStr">
+      <c r="B3" s="86" t="inlineStr">
         <is>
           <t>춘천 숙소 (2박)</t>
         </is>
       </c>
-      <c r="C3" s="195" t="inlineStr">
+      <c r="C3" s="86" t="inlineStr">
         <is>
           <t>8/3~5</t>
         </is>
       </c>
-      <c r="D3" s="197" t="inlineStr">
+      <c r="D3" s="86" t="inlineStr">
         <is>
           <t>야놀자/여기어때</t>
         </is>
       </c>
-      <c r="E3" s="197" t="inlineStr"/>
-      <c r="F3" s="197" t="inlineStr"/>
-      <c r="G3" s="197" t="inlineStr"/>
-      <c r="H3" s="196" t="inlineStr">
+      <c r="H3" s="86" t="inlineStr">
         <is>
           <t>웨이크보드 접근 편한 곳</t>
         </is>
       </c>
-      <c r="I3" s="195" t="inlineStr"/>
-      <c r="J3" s="195" t="inlineStr"/>
-      <c r="K3" s="195" t="inlineStr">
+      <c r="K3" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
+      <c r="L3" s="86" t="inlineStr">
+        <is>
+          <t>r0ec7f8d0</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1" s="87">
-      <c r="A4" s="195" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>숙박</t>
         </is>
       </c>
-      <c r="B4" s="196" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>강릉 경포 숙소</t>
         </is>
       </c>
-      <c r="C4" s="195" t="inlineStr">
+      <c r="C4" s="86" t="inlineStr">
         <is>
           <t>8/5~6</t>
         </is>
       </c>
-      <c r="D4" s="197" t="inlineStr">
+      <c r="D4" s="86" t="inlineStr">
         <is>
           <t>야놀자/여기어때</t>
         </is>
       </c>
-      <c r="E4" s="197" t="inlineStr"/>
-      <c r="F4" s="197" t="inlineStr"/>
-      <c r="G4" s="197" t="inlineStr"/>
-      <c r="H4" s="196" t="inlineStr">
+      <c r="H4" s="86" t="inlineStr">
         <is>
           <t>경포해변 근처</t>
         </is>
       </c>
-      <c r="I4" s="195" t="inlineStr"/>
-      <c r="J4" s="195" t="inlineStr"/>
-      <c r="K4" s="195" t="inlineStr">
+      <c r="K4" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
+      <c r="L4" s="86" t="inlineStr">
+        <is>
+          <t>r5dad96af</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1" s="87">
-      <c r="A5" s="195" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>숙박</t>
         </is>
       </c>
-      <c r="B5" s="196" t="inlineStr">
+      <c r="B5" s="86" t="inlineStr">
         <is>
           <t>경주 한옥 게스트하우스 (2박)</t>
         </is>
       </c>
-      <c r="C5" s="195" t="inlineStr">
+      <c r="C5" s="86" t="inlineStr">
         <is>
           <t>8/6~8</t>
         </is>
       </c>
-      <c r="D5" s="197" t="inlineStr">
+      <c r="D5" s="86" t="inlineStr">
         <is>
           <t>야놀자/여기어때</t>
         </is>
       </c>
-      <c r="E5" s="197" t="inlineStr"/>
-      <c r="F5" s="197" t="inlineStr"/>
-      <c r="G5" s="197" t="inlineStr"/>
-      <c r="H5" s="196" t="inlineStr">
+      <c r="H5" s="86" t="inlineStr">
         <is>
           <t>황남동 근처</t>
         </is>
       </c>
-      <c r="I5" s="195" t="inlineStr"/>
-      <c r="J5" s="195" t="inlineStr"/>
-      <c r="K5" s="195" t="inlineStr">
+      <c r="K5" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
+      <c r="L5" s="86" t="inlineStr">
+        <is>
+          <t>r76769a09</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1" s="87">
-      <c r="A6" s="195" t="inlineStr">
+      <c r="A6" s="86" t="inlineStr">
         <is>
           <t>숙박</t>
         </is>
       </c>
-      <c r="B6" s="196" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>부산 숙소 (2박)</t>
         </is>
       </c>
-      <c r="C6" s="195" t="inlineStr">
+      <c r="C6" s="86" t="inlineStr">
         <is>
           <t>8/8~10</t>
         </is>
       </c>
-      <c r="D6" s="197" t="inlineStr">
+      <c r="D6" s="86" t="inlineStr">
         <is>
           <t>야놀자/여기어때</t>
         </is>
       </c>
-      <c r="E6" s="197" t="inlineStr"/>
-      <c r="F6" s="197" t="inlineStr"/>
-      <c r="G6" s="197" t="inlineStr"/>
-      <c r="H6" s="196" t="inlineStr">
+      <c r="H6" s="86" t="inlineStr">
         <is>
           <t>남포동 or 해운대</t>
         </is>
       </c>
-      <c r="I6" s="195" t="inlineStr"/>
-      <c r="J6" s="195" t="inlineStr"/>
-      <c r="K6" s="195" t="inlineStr">
+      <c r="K6" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
+      <c r="L6" s="86" t="inlineStr">
+        <is>
+          <t>rbf9bcbb7</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1" s="87">
-      <c r="A7" s="195" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>숙박</t>
         </is>
       </c>
-      <c r="B7" s="196" t="inlineStr">
+      <c r="B7" s="86" t="inlineStr">
         <is>
           <t>통영 강구안 숙소</t>
         </is>
       </c>
-      <c r="C7" s="195" t="inlineStr">
+      <c r="C7" s="86" t="inlineStr">
         <is>
           <t>8/10~11</t>
         </is>
       </c>
-      <c r="D7" s="197" t="inlineStr">
+      <c r="D7" s="86" t="inlineStr">
         <is>
           <t>야놀자/여기어때</t>
         </is>
       </c>
-      <c r="E7" s="197" t="inlineStr"/>
-      <c r="F7" s="197" t="inlineStr"/>
-      <c r="G7" s="197" t="inlineStr"/>
-      <c r="H7" s="196" t="inlineStr">
+      <c r="H7" s="86" t="inlineStr">
         <is>
           <t>강구안 도보 5분 이내</t>
         </is>
       </c>
-      <c r="I7" s="195" t="inlineStr"/>
-      <c r="J7" s="195" t="inlineStr"/>
-      <c r="K7" s="195" t="inlineStr">
+      <c r="K7" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
+      <c r="L7" s="86" t="inlineStr">
+        <is>
+          <t>rebfa0d05</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1" s="87">
-      <c r="A8" s="195" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>숙박</t>
         </is>
       </c>
-      <c r="B8" s="196" t="inlineStr">
-        <is>
-          <t>전주 한옥 게스트하우스 (2박)</t>
-        </is>
-      </c>
-      <c r="C8" s="195" t="inlineStr">
-        <is>
-          <t>8/14~16</t>
-        </is>
-      </c>
-      <c r="D8" s="197" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
+        <is>
+          <t>포시즌펜션 (금오도 1박)</t>
+        </is>
+      </c>
+      <c r="C8" s="86" t="inlineStr">
+        <is>
+          <t>8/12~13</t>
+        </is>
+      </c>
+      <c r="D8" s="86" t="inlineStr">
+        <is>
+          <t>전화 예약 필수</t>
+        </is>
+      </c>
+      <c r="H8" s="86" t="inlineStr">
+        <is>
+          <t>비렁길 5코스 종점 장지 인근 · 전남 여수시 남면 금오로 1339-45</t>
+        </is>
+      </c>
+      <c r="K8" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L8" s="86" t="inlineStr">
+        <is>
+          <t>r5acd7b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="87">
+      <c r="A9" s="86" t="inlineStr">
+        <is>
+          <t>숙박</t>
+        </is>
+      </c>
+      <c r="B9" s="86" t="inlineStr">
+        <is>
+          <t>광주 숙소 (1박)</t>
+        </is>
+      </c>
+      <c r="C9" s="86" t="inlineStr">
+        <is>
+          <t>8/14~15</t>
+        </is>
+      </c>
+      <c r="D9" s="86" t="inlineStr">
         <is>
           <t>야놀자/여기어때</t>
         </is>
       </c>
-      <c r="E8" s="197" t="inlineStr"/>
-      <c r="F8" s="197" t="inlineStr"/>
-      <c r="G8" s="197" t="inlineStr"/>
-      <c r="H8" s="196" t="inlineStr">
-        <is>
-          <t>한옥마을 내부</t>
-        </is>
-      </c>
-      <c r="I8" s="195" t="inlineStr"/>
-      <c r="J8" s="195" t="inlineStr"/>
-      <c r="K8" s="195" t="inlineStr">
+      <c r="H9" s="86" t="inlineStr">
+        <is>
+          <t>유스퀘어 or 동구 중심부</t>
+        </is>
+      </c>
+      <c r="K9" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" s="87">
-      <c r="A9" s="195" t="inlineStr">
-        <is>
-          <t>숙박</t>
-        </is>
-      </c>
-      <c r="B9" s="196" t="inlineStr">
-        <is>
-          <t>단양 숙소</t>
-        </is>
-      </c>
-      <c r="C9" s="195" t="inlineStr">
-        <is>
-          <t>8/16~17</t>
-        </is>
-      </c>
-      <c r="D9" s="197" t="inlineStr">
-        <is>
-          <t>야놀자/여기어때</t>
-        </is>
-      </c>
-      <c r="E9" s="197" t="inlineStr"/>
-      <c r="F9" s="197" t="inlineStr"/>
-      <c r="G9" s="197" t="inlineStr"/>
-      <c r="H9" s="196" t="inlineStr">
-        <is>
-          <t>래프팅 업체 근처</t>
-        </is>
-      </c>
-      <c r="I9" s="195" t="inlineStr"/>
-      <c r="J9" s="195" t="inlineStr"/>
-      <c r="K9" s="195" t="inlineStr">
-        <is>
-          <t>☐</t>
+      <c r="L9" s="86" t="inlineStr">
+        <is>
+          <t>rdd126c83</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" s="87">
       <c r="A10" s="86" t="inlineStr">
         <is>
+          <t>숙박</t>
+        </is>
+      </c>
+      <c r="B10" s="86" t="inlineStr">
+        <is>
+          <t>단양 숙소</t>
+        </is>
+      </c>
+      <c r="C10" s="86" t="inlineStr">
+        <is>
+          <t>8/15~17</t>
+        </is>
+      </c>
+      <c r="D10" s="86" t="inlineStr">
+        <is>
+          <t>야놀자/여기어때</t>
+        </is>
+      </c>
+      <c r="H10" s="86" t="inlineStr">
+        <is>
+          <t>래프팅 업체 근처</t>
+        </is>
+      </c>
+      <c r="K10" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L10" s="86" t="inlineStr">
+        <is>
+          <t>re74a8ced</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="87">
+      <c r="A11" s="86" t="inlineStr">
+        <is>
           <t>교통</t>
         </is>
       </c>
-      <c r="B10" s="86" t="inlineStr">
-        <is>
-          <t>KTX 신경주→부산역</t>
-        </is>
-      </c>
-      <c r="C10" s="86" t="inlineStr">
-        <is>
-          <t>8/8</t>
-        </is>
-      </c>
-      <c r="D10" s="86" t="inlineStr">
-        <is>
-          <t>korail.com or 코레일 앱</t>
-        </is>
-      </c>
-      <c r="H10" s="86" t="inlineStr">
-        <is>
-          <t>경주 Day5 이동, 사전 예매 필수</t>
-        </is>
-      </c>
-      <c r="K10" s="86" t="inlineStr">
+      <c r="B11" s="86" t="inlineStr">
+        <is>
+          <t>여수→금오도 여객선 (신아해운)</t>
+        </is>
+      </c>
+      <c r="C11" s="86" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
+      <c r="D11" s="86" t="inlineStr">
+        <is>
+          <t>가보고싶은섬 온라인 예매</t>
+        </is>
+      </c>
+      <c r="H11" s="86" t="inlineStr">
+        <is>
+          <t>연안여객터미널 06:10 출발, 함구미 07:45 도착 · ⚠️ 성수기 사전 예매 필수</t>
+        </is>
+      </c>
+      <c r="K11" s="86" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" s="87">
-      <c r="A11" s="198" t="inlineStr">
-        <is>
-          <t>교통</t>
-        </is>
-      </c>
-      <c r="B11" s="199" t="inlineStr">
-        <is>
-          <t>금오도 여객선 (왕복)</t>
-        </is>
-      </c>
-      <c r="C11" s="198" t="inlineStr">
-        <is>
-          <t>8/12</t>
-        </is>
-      </c>
-      <c r="D11" s="200" t="inlineStr">
-        <is>
-          <t>여수연안여객터미널 현장</t>
-        </is>
-      </c>
-      <c r="E11" s="200" t="inlineStr"/>
-      <c r="F11" s="200" t="inlineStr"/>
-      <c r="G11" s="200" t="inlineStr"/>
-      <c r="H11" s="199" t="inlineStr">
-        <is>
-          <t>시간표 미리 확인</t>
-        </is>
-      </c>
-      <c r="I11" s="198" t="inlineStr"/>
-      <c r="J11" s="198" t="inlineStr"/>
-      <c r="K11" s="198" t="inlineStr">
-        <is>
-          <t>☐</t>
+      <c r="L11" s="86" t="inlineStr">
+        <is>
+          <t>r6c48a513</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="87">
       <c r="A12" s="86" t="inlineStr">
         <is>
-          <t>포시즌펜션 (금오도)</t>
+          <t>교통</t>
         </is>
       </c>
       <c r="B12" s="86" t="inlineStr">
         <is>
-          <t>8/12~13</t>
+          <t>안도→여수 여객선 (한림해운)</t>
         </is>
       </c>
       <c r="C12" s="86" t="inlineStr">
         <is>
-          <t>숙소</t>
+          <t>8/13</t>
         </is>
       </c>
       <c r="D12" s="86" t="inlineStr">
         <is>
+          <t>현장 발권</t>
+        </is>
+      </c>
+      <c r="H12" s="86" t="inlineStr">
+        <is>
+          <t>안도 선착장 16:40 출발 → 여수 연안터미널 ~18:10 도착 · ☎ 061-666-8092</t>
+        </is>
+      </c>
+      <c r="K12" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L12" s="86" t="inlineStr">
+        <is>
+          <t>r200da056</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="87">
+      <c r="A13" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B13" s="86" t="inlineStr">
+        <is>
+          <t>춘천 웨이크보드/모터보트</t>
+        </is>
+      </c>
+      <c r="C13" s="86" t="inlineStr">
+        <is>
+          <t>8/4</t>
+        </is>
+      </c>
+      <c r="D13" s="86" t="inlineStr">
+        <is>
+          <t>의암호 수상레저 전화/온라인</t>
+        </is>
+      </c>
+      <c r="H13" s="86" t="inlineStr">
+        <is>
+          <t>성수기 예약 권장</t>
+        </is>
+      </c>
+      <c r="K13" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L13" s="86" t="inlineStr">
+        <is>
+          <t>r20dc6272</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="87">
+      <c r="A14" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B14" s="86" t="inlineStr">
+        <is>
+          <t>통영 케이블카</t>
+        </is>
+      </c>
+      <c r="C14" s="86" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D14" s="86" t="inlineStr">
+        <is>
+          <t>현장 구매</t>
+        </is>
+      </c>
+      <c r="H14" s="86" t="inlineStr">
+        <is>
+          <t>성수기 대기 30분 예상</t>
+        </is>
+      </c>
+      <c r="K14" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L14" s="86" t="inlineStr">
+        <is>
+          <t>r2d74d4e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="87">
+      <c r="A15" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B15" s="86" t="inlineStr">
+        <is>
+          <t>한일관 저녁</t>
+        </is>
+      </c>
+      <c r="C15" s="86" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+      <c r="D15" s="86" t="inlineStr">
+        <is>
+          <t>전화 예약</t>
+        </is>
+      </c>
+      <c r="H15" s="86" t="inlineStr">
+        <is>
+          <t>⚠️ 반드시 사전 예약 · 2주 전 이상 권장</t>
+        </is>
+      </c>
+      <c r="K15" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L15" s="86" t="inlineStr">
+        <is>
+          <t>r21c5a557</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="87">
+      <c r="A16" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B16" s="86" t="inlineStr">
+        <is>
+          <t>남가정 (광주 한정식)</t>
+        </is>
+      </c>
+      <c r="C16" s="86" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D16" s="86" t="inlineStr">
+        <is>
           <t>전화 예약 필수</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" s="87">
-      <c r="A13" s="198" t="inlineStr">
+      <c r="H16" s="86" t="inlineStr">
+        <is>
+          <t>062-227-4114 · 광주 동구 지호로 137-7 · ⚠️ 광복절 연휴 저녁 18:00, 사전 예약 필수 · 월 휴무 (8/14 금 정상영업)</t>
+        </is>
+      </c>
+      <c r="K16" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L16" s="86" t="inlineStr">
+        <is>
+          <t>rb05fc1da</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="87">
+      <c r="A17" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B17" s="86" t="inlineStr">
+        <is>
+          <t>충주호 유람선 (장회나루)</t>
+        </is>
+      </c>
+      <c r="C17" s="86" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+      <c r="D17" s="86" t="inlineStr">
+        <is>
+          <t>장회나루 예약센터 (8월 일정 오픈 후 확인)</t>
+        </is>
+      </c>
+      <c r="H17" s="86" t="inlineStr">
+        <is>
+          <t>일요일 7회 출항 · 구담봉·옥순봉 코스 약 1.5시간 · ☎ 043-422-2772</t>
+        </is>
+      </c>
+      <c r="K17" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L17" s="86" t="inlineStr">
+        <is>
+          <t>ra332b4f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="87">
+      <c r="A18" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B18" s="86" t="inlineStr">
+        <is>
+          <t>단양 래프팅</t>
+        </is>
+      </c>
+      <c r="C18" s="86" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+      <c r="D18" s="86" t="inlineStr">
+        <is>
+          <t>단양 래프팅 업체 전화/온라인</t>
+        </is>
+      </c>
+      <c r="H18" s="86" t="inlineStr">
+        <is>
+          <t>⚠️ 성수기 조기 마감, 08:00 첫 타임 예약 필수</t>
+        </is>
+      </c>
+      <c r="K18" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L18" s="86" t="inlineStr">
+        <is>
+          <t>r29f79df0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="87">
+      <c r="A19" s="86" t="inlineStr">
+        <is>
+          <t>체험</t>
+        </is>
+      </c>
+      <c r="B19" s="86" t="inlineStr">
+        <is>
+          <t>충주 활옥동굴</t>
+        </is>
+      </c>
+      <c r="C19" s="86" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="D19" s="86" t="inlineStr">
+        <is>
+          <t>현장 구매 가능</t>
+        </is>
+      </c>
+      <c r="H19" s="86" t="inlineStr">
+        <is>
+          <t>내부 12°C — 겉옷 필수 · 보트 마감 16:00</t>
+        </is>
+      </c>
+      <c r="K19" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="L19" s="86" t="inlineStr">
+        <is>
+          <t>r530222a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="87">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>여행 준비</t>
+        </is>
+      </c>
+      <c r="B20" s="86" t="inlineStr">
+        <is>
+          <t>래쉬가드·수영복</t>
+        </is>
+      </c>
+      <c r="C20" s="86" t="inlineStr">
+        <is>
+          <t>출발 전</t>
+        </is>
+      </c>
+      <c r="D20" s="86" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="H20" s="86" t="inlineStr">
+        <is>
+          <t>웨이크보드·래프팅 필수</t>
+        </is>
+      </c>
+      <c r="K20" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="87">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>여행 준비</t>
+        </is>
+      </c>
+      <c r="B21" s="86" t="inlineStr">
+        <is>
+          <t>방수팩</t>
+        </is>
+      </c>
+      <c r="C21" s="86" t="inlineStr">
+        <is>
+          <t>출발 전</t>
+        </is>
+      </c>
+      <c r="D21" s="86" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="H21" s="86" t="inlineStr">
+        <is>
+          <t>래프팅·수상레저 핸드폰 보호</t>
+        </is>
+      </c>
+      <c r="K21" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="87">
+      <c r="A22" s="86" t="inlineStr">
+        <is>
+          <t>여행 준비</t>
+        </is>
+      </c>
+      <c r="B22" s="86" t="inlineStr">
+        <is>
+          <t>여행자보험</t>
+        </is>
+      </c>
+      <c r="C22" s="86" t="inlineStr">
+        <is>
+          <t>출발 전</t>
+        </is>
+      </c>
+      <c r="D22" s="86" t="inlineStr">
+        <is>
+          <t>보험사 앱</t>
+        </is>
+      </c>
+      <c r="H22" s="86" t="inlineStr">
+        <is>
+          <t>액티비티 다수 — 필수</t>
+        </is>
+      </c>
+      <c r="K22" s="86" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="87">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>교통</t>
         </is>
       </c>
-      <c r="B13" s="199" t="inlineStr">
-        <is>
-          <t>구례→전주 버스</t>
-        </is>
-      </c>
-      <c r="C13" s="198" t="inlineStr">
-        <is>
-          <t>8/14</t>
-        </is>
-      </c>
-      <c r="D13" s="200" t="inlineStr">
-        <is>
-          <t>고속버스 앱</t>
-        </is>
-      </c>
-      <c r="E13" s="200" t="inlineStr"/>
-      <c r="F13" s="200" t="inlineStr"/>
-      <c r="G13" s="200" t="inlineStr"/>
-      <c r="H13" s="199" t="inlineStr">
-        <is>
-          <t>광복절 전날 혼잡</t>
-        </is>
-      </c>
-      <c r="I13" s="198" t="inlineStr"/>
-      <c r="J13" s="198" t="inlineStr"/>
-      <c r="K13" s="198" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" s="87">
-      <c r="A14" s="198" t="inlineStr">
-        <is>
-          <t>교통</t>
-        </is>
-      </c>
-      <c r="B14" s="199" t="inlineStr">
-        <is>
-          <t>전주→단양 버스</t>
-        </is>
-      </c>
-      <c r="C14" s="198" t="inlineStr">
-        <is>
-          <t>8/16</t>
-        </is>
-      </c>
-      <c r="D14" s="200" t="inlineStr">
-        <is>
-          <t>고속버스 앱</t>
-        </is>
-      </c>
-      <c r="E14" s="200" t="inlineStr"/>
-      <c r="F14" s="200" t="inlineStr"/>
-      <c r="G14" s="200" t="inlineStr"/>
-      <c r="H14" s="199" t="inlineStr">
-        <is>
-          <t>청주 경유, 사전 예약</t>
-        </is>
-      </c>
-      <c r="I14" s="198" t="inlineStr"/>
-      <c r="J14" s="198" t="inlineStr"/>
-      <c r="K14" s="198" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" s="87">
-      <c r="A15" s="198" t="inlineStr">
-        <is>
-          <t>교통</t>
-        </is>
-      </c>
-      <c r="B15" s="199" t="inlineStr">
-        <is>
-          <t>단양→서울 버스</t>
-        </is>
-      </c>
-      <c r="C15" s="198" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="D15" s="200" t="inlineStr">
-        <is>
-          <t>고속버스 앱</t>
-        </is>
-      </c>
-      <c r="E15" s="200" t="inlineStr"/>
-      <c r="F15" s="200" t="inlineStr"/>
-      <c r="G15" s="200" t="inlineStr"/>
-      <c r="H15" s="199" t="inlineStr">
-        <is>
-          <t>마지막날 귀경</t>
-        </is>
-      </c>
-      <c r="I15" s="198" t="inlineStr"/>
-      <c r="J15" s="198" t="inlineStr"/>
-      <c r="K15" s="198" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" s="87">
-      <c r="A16" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B16" s="202" t="inlineStr">
-        <is>
-          <t>춘천 웨이크보드/모터보트</t>
-        </is>
-      </c>
-      <c r="C16" s="201" t="inlineStr">
-        <is>
-          <t>8/4</t>
-        </is>
-      </c>
-      <c r="D16" s="203" t="inlineStr">
-        <is>
-          <t>의암호 수상레저 전화/온라인</t>
-        </is>
-      </c>
-      <c r="E16" s="203" t="inlineStr"/>
-      <c r="F16" s="203" t="inlineStr"/>
-      <c r="G16" s="203" t="inlineStr"/>
-      <c r="H16" s="202" t="inlineStr">
-        <is>
-          <t>성수기 예약 권장</t>
-        </is>
-      </c>
-      <c r="I16" s="201" t="inlineStr"/>
-      <c r="J16" s="201" t="inlineStr"/>
-      <c r="K16" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="87">
-      <c r="A17" s="201" t="n"/>
-      <c r="B17" s="202" t="n"/>
-      <c r="C17" s="201" t="n"/>
-      <c r="D17" s="203" t="n"/>
-      <c r="E17" s="203" t="n"/>
-      <c r="F17" s="203" t="n"/>
-      <c r="G17" s="203" t="n"/>
-      <c r="H17" s="202" t="n"/>
-      <c r="I17" s="201" t="n"/>
-      <c r="J17" s="201" t="n"/>
-      <c r="K17" s="201" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="87">
-      <c r="A18" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B18" s="202" t="inlineStr">
-        <is>
-          <t>통영 케이블카</t>
-        </is>
-      </c>
-      <c r="C18" s="201" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
-      <c r="D18" s="203" t="inlineStr">
-        <is>
-          <t>현장 구매</t>
-        </is>
-      </c>
-      <c r="E18" s="203" t="inlineStr"/>
-      <c r="F18" s="203" t="inlineStr"/>
-      <c r="G18" s="203" t="inlineStr"/>
-      <c r="H18" s="202" t="inlineStr">
-        <is>
-          <t>성수기 대기 30분 예상</t>
-        </is>
-      </c>
-      <c r="I18" s="201" t="inlineStr"/>
-      <c r="J18" s="201" t="inlineStr"/>
-      <c r="K18" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="87">
-      <c r="A19" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B19" s="202" t="inlineStr">
-        <is>
-          <t>한일관 저녁</t>
-        </is>
-      </c>
-      <c r="C19" s="201" t="inlineStr">
-        <is>
-          <t>8/11</t>
-        </is>
-      </c>
-      <c r="D19" s="203" t="inlineStr">
-        <is>
-          <t>전화 예약</t>
-        </is>
-      </c>
-      <c r="E19" s="203" t="inlineStr"/>
-      <c r="F19" s="203" t="inlineStr"/>
-      <c r="G19" s="203" t="inlineStr"/>
-      <c r="H19" s="202" t="inlineStr">
-        <is>
-          <t>⚠️ 반드시 사전 예약</t>
-        </is>
-      </c>
-      <c r="I19" s="201" t="inlineStr"/>
-      <c r="J19" s="201" t="inlineStr"/>
-      <c r="K19" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="87">
-      <c r="A20" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B20" s="202" t="inlineStr">
-        <is>
-          <t>전주 한정식 점심</t>
-        </is>
-      </c>
-      <c r="C20" s="201" t="inlineStr">
-        <is>
-          <t>8/16</t>
-        </is>
-      </c>
-      <c r="D20" s="203" t="inlineStr">
-        <is>
-          <t>전화 예약</t>
-        </is>
-      </c>
-      <c r="E20" s="203" t="inlineStr"/>
-      <c r="F20" s="203" t="inlineStr"/>
-      <c r="G20" s="203" t="inlineStr"/>
-      <c r="H20" s="202" t="inlineStr">
-        <is>
-          <t>인기 식당 사전 예약 필수</t>
-        </is>
-      </c>
-      <c r="I20" s="201" t="inlineStr"/>
-      <c r="J20" s="201" t="inlineStr"/>
-      <c r="K20" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" s="87">
-      <c r="A21" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B21" s="202" t="inlineStr">
-        <is>
-          <t>단양 래프팅</t>
-        </is>
-      </c>
-      <c r="C21" s="201" t="inlineStr">
-        <is>
-          <t>8/16</t>
-        </is>
-      </c>
-      <c r="D21" s="203" t="inlineStr">
-        <is>
-          <t>단양 래프팅 업체 전화/온라인</t>
-        </is>
-      </c>
-      <c r="E21" s="203" t="inlineStr"/>
-      <c r="F21" s="203" t="inlineStr"/>
-      <c r="G21" s="203" t="inlineStr"/>
-      <c r="H21" s="202" t="inlineStr">
-        <is>
-          <t>⚠️ 성수기 조기 마감</t>
-        </is>
-      </c>
-      <c r="I21" s="201" t="inlineStr"/>
-      <c r="J21" s="201" t="inlineStr"/>
-      <c r="K21" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" s="87">
-      <c r="A22" s="201" t="inlineStr">
-        <is>
-          <t>체험</t>
-        </is>
-      </c>
-      <c r="B22" s="202" t="inlineStr">
-        <is>
-          <t>충주 활옥동굴</t>
-        </is>
-      </c>
-      <c r="C22" s="201" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="D22" s="203" t="inlineStr">
-        <is>
-          <t>현장 구매 가능</t>
-        </is>
-      </c>
-      <c r="E22" s="203" t="inlineStr"/>
-      <c r="F22" s="203" t="inlineStr"/>
-      <c r="G22" s="203" t="inlineStr"/>
-      <c r="H22" s="202" t="inlineStr">
-        <is>
-          <t>내부 12°C — 겉옷 필수</t>
-        </is>
-      </c>
-      <c r="I22" s="201" t="inlineStr"/>
-      <c r="J22" s="201" t="inlineStr"/>
-      <c r="K22" s="201" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" s="87">
-      <c r="A23" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B23" s="205" t="inlineStr">
-        <is>
-          <t>래쉬가드·수영복</t>
-        </is>
-      </c>
-      <c r="C23" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D23" s="206" t="inlineStr">
-        <is>
-          <t>구매</t>
-        </is>
-      </c>
-      <c r="E23" s="206" t="inlineStr"/>
-      <c r="F23" s="206" t="inlineStr"/>
-      <c r="G23" s="206" t="inlineStr"/>
-      <c r="H23" s="205" t="inlineStr">
-        <is>
-          <t>웨이크보드·래프팅 필수</t>
-        </is>
-      </c>
-      <c r="I23" s="204" t="inlineStr"/>
-      <c r="J23" s="204" t="inlineStr"/>
-      <c r="K23" s="204" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" s="87">
-      <c r="A24" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B24" s="205" t="inlineStr">
-        <is>
-          <t>방수팩</t>
-        </is>
-      </c>
-      <c r="C24" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D24" s="206" t="inlineStr">
-        <is>
-          <t>구매</t>
-        </is>
-      </c>
-      <c r="E24" s="206" t="inlineStr"/>
-      <c r="F24" s="206" t="inlineStr"/>
-      <c r="G24" s="206" t="inlineStr"/>
-      <c r="H24" s="205" t="inlineStr">
-        <is>
-          <t>래프팅·수상레저 핸드폰 보호</t>
-        </is>
-      </c>
-      <c r="I24" s="204" t="inlineStr"/>
-      <c r="J24" s="204" t="inlineStr"/>
-      <c r="K24" s="204" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="87">
-      <c r="A25" s="204" t="inlineStr">
-        <is>
-          <t>여행 준비</t>
-        </is>
-      </c>
-      <c r="B25" s="205" t="inlineStr">
-        <is>
-          <t>여행자보험</t>
-        </is>
-      </c>
-      <c r="C25" s="204" t="inlineStr">
-        <is>
-          <t>출발 전</t>
-        </is>
-      </c>
-      <c r="D25" s="206" t="inlineStr">
-        <is>
-          <t>보험사 앱</t>
-        </is>
-      </c>
-      <c r="E25" s="206" t="inlineStr"/>
-      <c r="F25" s="206" t="inlineStr"/>
-      <c r="G25" s="206" t="inlineStr"/>
-      <c r="H25" s="205" t="inlineStr">
-        <is>
-          <t>액티비티 다수 — 필수</t>
-        </is>
-      </c>
-      <c r="I25" s="204" t="inlineStr"/>
-      <c r="J25" s="204" t="inlineStr"/>
-      <c r="K25" s="204" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
+      <c r="B23" s="86" t="inlineStr">
+        <is>
+          <t>자차 (아이오닉6)</t>
+        </is>
+      </c>
+      <c r="C23" s="86" t="inlineStr">
+        <is>
+          <t>전 일정</t>
+        </is>
+      </c>
+      <c r="D23" s="86" t="inlineStr">
+        <is>
+          <t>사전 점검 권장</t>
+        </is>
+      </c>
+      <c r="H23" s="86" t="inlineStr">
+        <is>
+          <t>전 구간 자차 이동 · 주요 충전: 강릉출발 전·광주출발 전·단양 · 총 이동거리 약 1,500km</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="87"/>
+    <row r="25" ht="22" customHeight="1" s="87"/>
     <row r="26" ht="22" customHeight="1" s="87"/>
     <row r="27" ht="22" customHeight="1" s="87"/>
     <row r="28" ht="19.5" customHeight="1" s="87"/>
@@ -4239,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="86" min="1" max="2"/>
@@ -5871,6 +5892,350 @@
         </is>
       </c>
       <c r="G46" s="86" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="207" t="inlineStr">
+        <is>
+          <t>광주
+(Day12)</t>
+        </is>
+      </c>
+      <c r="B47" s="207" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="C47" s="207" t="inlineStr">
+        <is>
+          <t>남가정</t>
+        </is>
+      </c>
+      <c r="D47" s="207" t="inlineStr">
+        <is>
+          <t>돼지떡갈비 정식 26,000원 / 한우떡갈비 34,000원</t>
+        </is>
+      </c>
+      <c r="E47" s="207" t="inlineStr">
+        <is>
+          <t>국가공인 조리기능장 3대째 운영. 100% 고기 수제 떡갈비·솥밥 코스. 흑임자죽 → 샐러드 → 오골계삼계탕 → 수제 떡갈비 → 솥밥 순. 무료주차·개별룸 가능. ☎ 062-227-4114 (광복절 연휴 저녁 예약 필수)</t>
+        </is>
+      </c>
+      <c r="F47" s="207" t="inlineStr">
+        <is>
+          <t>광주 동구 지호로 137-7 (지산동)</t>
+        </is>
+      </c>
+      <c r="G47" s="208" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="207" t="inlineStr">
+        <is>
+          <t>광주
+(Day12)</t>
+        </is>
+      </c>
+      <c r="B48" s="207" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="C48" s="207" t="inlineStr">
+        <is>
+          <t>무등분식</t>
+        </is>
+      </c>
+      <c r="D48" s="207" t="inlineStr">
+        <is>
+          <t>상추튀김·떡볶이·순대</t>
+        </is>
+      </c>
+      <c r="E48" s="207" t="inlineStr">
+        <is>
+          <t>★광주 7미 노포★ 금남로5가 인근 20년 영업. 백반기행·수요미식회 소개. 오징어·야채튀김을 상추에 싸먹는 광주 명물. 학생·현지인 단골. 가성비 최상</t>
+        </is>
+      </c>
+      <c r="F48" s="207" t="inlineStr">
+        <is>
+          <t>광주 북구 독립로 249</t>
+        </is>
+      </c>
+      <c r="G48" s="208" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="207" t="inlineStr">
+        <is>
+          <t>광주
+(Day12)</t>
+        </is>
+      </c>
+      <c r="B49" s="207" t="inlineStr">
+        <is>
+          <t>점심/저녁 추가</t>
+        </is>
+      </c>
+      <c r="C49" s="207" t="inlineStr">
+        <is>
+          <t>팔도강산</t>
+        </is>
+      </c>
+      <c r="D49" s="207" t="inlineStr">
+        <is>
+          <t>무등산 보리밥정식·계절 나물</t>
+        </is>
+      </c>
+      <c r="E49" s="207" t="inlineStr">
+        <is>
+          <t>무등산 지산유원지 보리밥거리 대표 식당. 제철 나물 10여 종 + 된장찌개 한 상. 등산객·현지인 모두 찾는 거리 터줏대감. 보리밥거리 내 가장 오래된 집 중 하나</t>
+        </is>
+      </c>
+      <c r="F49" s="207" t="inlineStr">
+        <is>
+          <t>광주 동구 지호로 137-3</t>
+        </is>
+      </c>
+      <c r="G49" s="208" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="209" t="inlineStr">
+        <is>
+          <t>충주
+(Day13)</t>
+        </is>
+      </c>
+      <c r="B50" s="209" t="inlineStr">
+        <is>
+          <t>아침/점심</t>
+        </is>
+      </c>
+      <c r="C50" s="209" t="inlineStr">
+        <is>
+          <t>운정식당</t>
+        </is>
+      </c>
+      <c r="D50" s="209" t="inlineStr">
+        <is>
+          <t>올갱이해장국·육개장</t>
+        </is>
+      </c>
+      <c r="E50" s="209" t="inlineStr">
+        <is>
+          <t>★50년 넘은 충주 노포★ 각종 방송 프로그램 소개. 충주 재래시장 인근. 남한강 다슬기(올갱이)로 끓인 진한 해장국. 현지인 아침 해장 성지. 06:00 이른 오픈</t>
+        </is>
+      </c>
+      <c r="F50" s="209" t="inlineStr">
+        <is>
+          <t>충북 충주시 중원대로 3432-1</t>
+        </is>
+      </c>
+      <c r="G50" s="210" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="209" t="inlineStr">
+        <is>
+          <t>충주
+(Day13)</t>
+        </is>
+      </c>
+      <c r="B51" s="209" t="inlineStr">
+        <is>
+          <t>점심 추가</t>
+        </is>
+      </c>
+      <c r="C51" s="209" t="inlineStr">
+        <is>
+          <t>남한강물고기</t>
+        </is>
+      </c>
+      <c r="D51" s="209" t="inlineStr">
+        <is>
+          <t>남한강 민물 매운탕·송어회</t>
+        </is>
+      </c>
+      <c r="E51" s="209" t="inlineStr">
+        <is>
+          <t>충주호 인근 현지인이 찾는 민물어 전문점. 남한강에서 잡은 쏘가리·메기·잉어 매운탕. 단양 진입 전 충주 마지막 로컬 식사 포인트</t>
+        </is>
+      </c>
+      <c r="F51" s="209" t="inlineStr">
+        <is>
+          <t>충북 충주시 상봉동 일대</t>
+        </is>
+      </c>
+      <c r="G51" s="210" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="211" t="inlineStr">
+        <is>
+          <t>단양
+(Day13~15)</t>
+        </is>
+      </c>
+      <c r="B52" s="211" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="C52" s="211" t="inlineStr">
+        <is>
+          <t>어부명가</t>
+        </is>
+      </c>
+      <c r="D52" s="211" t="inlineStr">
+        <is>
+          <t>쏘가리 매운탕·마늘떡갈비</t>
+        </is>
+      </c>
+      <c r="E52" s="211" t="inlineStr">
+        <is>
+          <t>★단양팔경 어업허가 35년 노포★ 직접 잡은 남한강 쏘가리로 끓이는 매운탕. 단양군 쏘가리특화거리 선정업소. 마늘떡갈비도 명물. 현지인·방문객 모두 인정</t>
+        </is>
+      </c>
+      <c r="F52" s="211" t="inlineStr">
+        <is>
+          <t>충북 단양군 단양읍 수변로 87</t>
+        </is>
+      </c>
+      <c r="G52" s="212" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="211" t="inlineStr">
+        <is>
+          <t>단양
+(Day13~15)</t>
+        </is>
+      </c>
+      <c r="B53" s="211" t="inlineStr">
+        <is>
+          <t>저녁/점심</t>
+        </is>
+      </c>
+      <c r="C53" s="211" t="inlineStr">
+        <is>
+          <t>원조마늘순대 (구경시장)</t>
+        </is>
+      </c>
+      <c r="D53" s="211" t="inlineStr">
+        <is>
+          <t>마늘순대국밥·마늘순대</t>
+        </is>
+      </c>
+      <c r="E53" s="211" t="inlineStr">
+        <is>
+          <t>단양구경시장 내 원조 마늘순대 노포. 단양 특산 마늘을 넣은 순대국밥. 시장 상인·현지인 단골. 구경시장 5일장날(1·6일) 특히 붐빔</t>
+        </is>
+      </c>
+      <c r="F53" s="211" t="inlineStr">
+        <is>
+          <t>충북 단양군 단양읍 도전6길 29 (구경시장 내)</t>
+        </is>
+      </c>
+      <c r="G53" s="212" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="211" t="inlineStr">
+        <is>
+          <t>단양
+(Day13~15)</t>
+        </is>
+      </c>
+      <c r="B54" s="211" t="inlineStr">
+        <is>
+          <t>아침/점심</t>
+        </is>
+      </c>
+      <c r="C54" s="211" t="inlineStr">
+        <is>
+          <t>남한강 올갱이국밥 일대
+(구경시장 주변)</t>
+        </is>
+      </c>
+      <c r="D54" s="211" t="inlineStr">
+        <is>
+          <t>올갱이국밥·올갱이파전</t>
+        </is>
+      </c>
+      <c r="E54" s="211" t="inlineStr">
+        <is>
+          <t>단양구경시장 주변 올갱이(다슬기) 국밥 전문점 골목. 남한강 상류 1급수 다슬기로 끓인 향토 음식. 단양 현지인 아침 단골 코스. 그집쏘가리 방문 시 올갱이파전 서비스 제공</t>
+        </is>
+      </c>
+      <c r="F54" s="211" t="inlineStr">
+        <is>
+          <t>충북 단양군 단양읍 구경시장 일원</t>
+        </is>
+      </c>
+      <c r="G54" s="212" t="inlineStr">
+        <is>
+          <t>📍 지도에서 보기</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="86" t="inlineStr">
+        <is>
+          <t>전남
+담양</t>
+        </is>
+      </c>
+      <c r="B55" s="86" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="C55" s="86" t="inlineStr">
+        <is>
+          <t>담양 떡갈비
+(담양 읍내 노포)</t>
+        </is>
+      </c>
+      <c r="D55" s="86" t="inlineStr">
+        <is>
+          <t>소·돼지 합육 떡갈비·공깃밥</t>
+        </is>
+      </c>
+      <c r="E55" s="86" t="inlineStr">
+        <is>
+          <t>담양 읍내 떡갈비 골목 현지인 노포. 직접 고기를 다지고 빚어 구운 정통 방식. 30~40년 영업. 관광객 줄 서는 집 아닌 동네 단골집</t>
+        </is>
+      </c>
+      <c r="F55" s="86" t="inlineStr">
+        <is>
+          <t>전남 담양군 담양읍 담양로 일원</t>
+        </is>
+      </c>
+      <c r="G55" s="86" t="inlineStr">
         <is>
           <t>📍 지도에서 보기</t>
         </is>
